--- a/statistics_files/2026/2026_99_gc_sharing.xlsx
+++ b/statistics_files/2026/2026_99_gc_sharing.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{5EB0D5A8-5FF4-4EDE-A07D-38280A5772B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF82C4D-4917-41A1-B177-BCBADF5BC8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -42,8 +42,17 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">September!$A$1:$D$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Yearly total'!$A$1:$D$56</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -234,7 +243,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1137,7 +1146,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1923,13 +1932,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D56" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2411,13 +2420,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D56" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2899,13 +2908,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D56" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3387,13 +3396,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D56" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4352,13 +4361,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D56" xr:uid="{00000000-0009-0000-0000-00000C000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4840,13 +4849,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D56" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5328,13 +5337,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D56" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5816,13 +5825,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D56" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6304,13 +6313,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D56" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6792,13 +6801,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D56" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7280,13 +7289,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D56" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7768,13 +7777,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D56" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8256,7 +8265,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D56" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/statistics_files/2026/2026_99_gc_sharing.xlsx
+++ b/statistics_files/2026/2026_99_gc_sharing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF82C4D-4917-41A1-B177-BCBADF5BC8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41656763-E07E-4ACE-BE34-0C5981AF8371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3431,15 +3431,15 @@
       </c>
       <c r="B2" s="3">
         <f>SUM(January:December!B2)</f>
-        <v>4222</v>
+        <v>7978</v>
       </c>
       <c r="C2" s="3">
         <f>SUM(January:December!C2)</f>
-        <v>1441</v>
+        <v>2807</v>
       </c>
       <c r="D2" s="3">
         <f>SUM(January:December!D2)</f>
-        <v>5663</v>
+        <v>10785</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3448,15 +3448,15 @@
       </c>
       <c r="B3" s="4">
         <f>SUM(January:December!B3)</f>
-        <v>2584</v>
+        <v>4978</v>
       </c>
       <c r="C3" s="4">
         <f>SUM(January:December!C3)</f>
-        <v>671</v>
+        <v>1343</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(January:December!D3)</f>
-        <v>3255</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3465,15 +3465,15 @@
       </c>
       <c r="B4" s="3">
         <f>SUM(January:December!B4)</f>
-        <v>7786</v>
+        <v>14710</v>
       </c>
       <c r="C4" s="3">
         <f>SUM(January:December!C4)</f>
-        <v>1369</v>
+        <v>2509</v>
       </c>
       <c r="D4" s="3">
         <f>SUM(January:December!D4)</f>
-        <v>9155</v>
+        <v>17219</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3482,15 +3482,15 @@
       </c>
       <c r="B5" s="4">
         <f>SUM(January:December!B5)</f>
-        <v>61</v>
+        <v>145</v>
       </c>
       <c r="C5" s="4">
         <f>SUM(January:December!C5)</f>
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D5" s="4">
         <f>SUM(January:December!D5)</f>
-        <v>89</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3499,15 +3499,15 @@
       </c>
       <c r="B6" s="3">
         <f>SUM(January:December!B6)</f>
-        <v>5110</v>
+        <v>9794</v>
       </c>
       <c r="C6" s="3">
         <f>SUM(January:December!C6)</f>
-        <v>1162</v>
+        <v>2128</v>
       </c>
       <c r="D6" s="3">
         <f>SUM(January:December!D6)</f>
-        <v>6272</v>
+        <v>11922</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3516,15 +3516,15 @@
       </c>
       <c r="B7" s="4">
         <f>SUM(January:December!B7)</f>
-        <v>845</v>
+        <v>1573</v>
       </c>
       <c r="C7" s="4">
         <f>SUM(January:December!C7)</f>
-        <v>217</v>
+        <v>386</v>
       </c>
       <c r="D7" s="4">
         <f>SUM(January:December!D7)</f>
-        <v>1062</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3533,15 +3533,15 @@
       </c>
       <c r="B8" s="3">
         <f>SUM(January:December!B8)</f>
-        <v>374</v>
+        <v>865</v>
       </c>
       <c r="C8" s="3">
         <f>SUM(January:December!C8)</f>
-        <v>111</v>
+        <v>218</v>
       </c>
       <c r="D8" s="3">
         <f>SUM(January:December!D8)</f>
-        <v>485</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3550,15 +3550,15 @@
       </c>
       <c r="B9" s="4">
         <f>SUM(January:December!B9)</f>
-        <v>178</v>
+        <v>336</v>
       </c>
       <c r="C9" s="4">
         <f>SUM(January:December!C9)</f>
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="D9" s="4">
         <f>SUM(January:December!D9)</f>
-        <v>251</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3567,15 +3567,15 @@
       </c>
       <c r="B10" s="3">
         <f>SUM(January:December!B10)</f>
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="C10" s="3">
         <f>SUM(January:December!C10)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3">
         <f>SUM(January:December!D10)</f>
-        <v>53</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3601,15 +3601,15 @@
       </c>
       <c r="B12" s="5">
         <f>SUM(January:December!B12)</f>
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C12" s="5">
         <f>SUM(January:December!C12)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D12" s="5">
         <f>SUM(January:December!D12)</f>
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3618,15 +3618,15 @@
       </c>
       <c r="B13" s="6">
         <f>SUM(January:December!B13)</f>
-        <v>108</v>
+        <v>181</v>
       </c>
       <c r="C13" s="6">
         <f>SUM(January:December!C13)</f>
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D13" s="6">
         <f>SUM(January:December!D13)</f>
-        <v>150</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3635,15 +3635,15 @@
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>577</v>
+        <v>1173</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>168</v>
+        <v>294</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>745</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3652,15 +3652,15 @@
       </c>
       <c r="B15" s="6">
         <f>SUM(January:December!B15)</f>
-        <v>315</v>
+        <v>495</v>
       </c>
       <c r="C15" s="6">
         <f>SUM(January:December!C15)</f>
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="D15" s="6">
         <f>SUM(January:December!D15)</f>
-        <v>370</v>
+        <v>596</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3669,15 +3669,15 @@
       </c>
       <c r="B16" s="3">
         <f>SUM(January:December!B16)</f>
-        <v>172</v>
+        <v>406</v>
       </c>
       <c r="C16" s="3">
         <f>SUM(January:December!C16)</f>
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D16" s="3">
         <f>SUM(January:December!D16)</f>
-        <v>246</v>
+        <v>540</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3686,15 +3686,15 @@
       </c>
       <c r="B17" s="4">
         <f>SUM(January:December!B17)</f>
-        <v>1204</v>
+        <v>2274</v>
       </c>
       <c r="C17" s="4">
         <f>SUM(January:December!C17)</f>
-        <v>694</v>
+        <v>1422</v>
       </c>
       <c r="D17" s="4">
         <f>SUM(January:December!D17)</f>
-        <v>1898</v>
+        <v>3696</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3703,15 +3703,15 @@
       </c>
       <c r="B18" s="3">
         <f>SUM(January:December!B18)</f>
-        <v>90</v>
+        <v>181</v>
       </c>
       <c r="C18" s="3">
         <f>SUM(January:December!C18)</f>
-        <v>89</v>
+        <v>203</v>
       </c>
       <c r="D18" s="3">
         <f>SUM(January:December!D18)</f>
-        <v>179</v>
+        <v>384</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3720,15 +3720,15 @@
       </c>
       <c r="B19" s="4">
         <f>SUM(January:December!B19)</f>
-        <v>1547</v>
+        <v>3169</v>
       </c>
       <c r="C19" s="4">
         <f>SUM(January:December!C19)</f>
-        <v>485</v>
+        <v>1209</v>
       </c>
       <c r="D19" s="4">
         <f>SUM(January:December!D19)</f>
-        <v>2032</v>
+        <v>4378</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3737,15 +3737,15 @@
       </c>
       <c r="B20" s="3">
         <f>SUM(January:December!B20)</f>
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C20" s="3">
         <f>SUM(January:December!C20)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D20" s="3">
         <f>SUM(January:December!D20)</f>
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3754,15 +3754,15 @@
       </c>
       <c r="B21" s="4">
         <f>SUM(January:December!B21)</f>
-        <v>1517</v>
+        <v>2866</v>
       </c>
       <c r="C21" s="4">
         <f>SUM(January:December!C21)</f>
-        <v>501</v>
+        <v>949</v>
       </c>
       <c r="D21" s="4">
         <f>SUM(January:December!D21)</f>
-        <v>2018</v>
+        <v>3815</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3771,15 +3771,15 @@
       </c>
       <c r="B22" s="3">
         <f>SUM(January:December!B22)</f>
-        <v>223</v>
+        <v>422</v>
       </c>
       <c r="C22" s="3">
         <f>SUM(January:December!C22)</f>
-        <v>90</v>
+        <v>219</v>
       </c>
       <c r="D22" s="3">
         <f>SUM(January:December!D22)</f>
-        <v>313</v>
+        <v>641</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3788,15 +3788,15 @@
       </c>
       <c r="B23" s="4">
         <f>SUM(January:December!B23)</f>
-        <v>1917</v>
+        <v>3849</v>
       </c>
       <c r="C23" s="4">
         <f>SUM(January:December!C23)</f>
-        <v>613</v>
+        <v>1194</v>
       </c>
       <c r="D23" s="4">
         <f>SUM(January:December!D23)</f>
-        <v>2530</v>
+        <v>5043</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3805,15 +3805,15 @@
       </c>
       <c r="B24" s="3">
         <f>SUM(January:December!B24)</f>
-        <v>9496</v>
+        <v>18585</v>
       </c>
       <c r="C24" s="3">
         <f>SUM(January:December!C24)</f>
-        <v>1809</v>
+        <v>3710</v>
       </c>
       <c r="D24" s="3">
         <f>SUM(January:December!D24)</f>
-        <v>11305</v>
+        <v>22295</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3822,15 +3822,15 @@
       </c>
       <c r="B25" s="4">
         <f>SUM(January:December!B25)</f>
-        <v>406</v>
+        <v>797</v>
       </c>
       <c r="C25" s="4">
         <f>SUM(January:December!C25)</f>
-        <v>172</v>
+        <v>346</v>
       </c>
       <c r="D25" s="4">
         <f>SUM(January:December!D25)</f>
-        <v>578</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3856,15 +3856,15 @@
       </c>
       <c r="B27" s="4">
         <f>SUM(January:December!B27)</f>
-        <v>410</v>
+        <v>761</v>
       </c>
       <c r="C27" s="4">
         <f>SUM(January:December!C27)</f>
-        <v>231</v>
+        <v>403</v>
       </c>
       <c r="D27" s="4">
         <f>SUM(January:December!D27)</f>
-        <v>641</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3873,15 +3873,15 @@
       </c>
       <c r="B28" s="3">
         <f>SUM(January:December!B28)</f>
-        <v>327</v>
+        <v>643</v>
       </c>
       <c r="C28" s="3">
         <f>SUM(January:December!C28)</f>
-        <v>132</v>
+        <v>258</v>
       </c>
       <c r="D28" s="3">
         <f>SUM(January:December!D28)</f>
-        <v>459</v>
+        <v>901</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3890,15 +3890,15 @@
       </c>
       <c r="B29" s="4">
         <f>SUM(January:December!B29)</f>
-        <v>1689</v>
+        <v>3195</v>
       </c>
       <c r="C29" s="4">
         <f>SUM(January:December!C29)</f>
-        <v>891</v>
+        <v>1761</v>
       </c>
       <c r="D29" s="4">
         <f>SUM(January:December!D29)</f>
-        <v>2580</v>
+        <v>4956</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3907,15 +3907,15 @@
       </c>
       <c r="B30" s="3">
         <f>SUM(January:December!B30)</f>
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C30" s="3">
         <f>SUM(January:December!C30)</f>
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D30" s="3">
         <f>SUM(January:December!D30)</f>
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3924,15 +3924,15 @@
       </c>
       <c r="B31" s="4">
         <f>SUM(January:December!B31)</f>
-        <v>375</v>
+        <v>707</v>
       </c>
       <c r="C31" s="4">
         <f>SUM(January:December!C31)</f>
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="D31" s="4">
         <f>SUM(January:December!D31)</f>
-        <v>494</v>
+        <v>965</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3941,15 +3941,15 @@
       </c>
       <c r="B32" s="3">
         <f>SUM(January:December!B32)</f>
-        <v>1269</v>
+        <v>2387</v>
       </c>
       <c r="C32" s="3">
         <f>SUM(January:December!C32)</f>
-        <v>521</v>
+        <v>920</v>
       </c>
       <c r="D32" s="3">
         <f>SUM(January:December!D32)</f>
-        <v>1790</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3958,15 +3958,15 @@
       </c>
       <c r="B33" s="4">
         <f>SUM(January:December!B33)</f>
-        <v>688</v>
+        <v>1445</v>
       </c>
       <c r="C33" s="4">
         <f>SUM(January:December!C33)</f>
-        <v>373</v>
+        <v>757</v>
       </c>
       <c r="D33" s="4">
         <f>SUM(January:December!D33)</f>
-        <v>1061</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3975,15 +3975,15 @@
       </c>
       <c r="B34" s="3">
         <f>SUM(January:December!B34)</f>
-        <v>437</v>
+        <v>1028</v>
       </c>
       <c r="C34" s="3">
         <f>SUM(January:December!C34)</f>
-        <v>208</v>
+        <v>432</v>
       </c>
       <c r="D34" s="3">
         <f>SUM(January:December!D34)</f>
-        <v>645</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3992,15 +3992,15 @@
       </c>
       <c r="B35" s="4">
         <f>SUM(January:December!B35)</f>
-        <v>5970</v>
+        <v>11448</v>
       </c>
       <c r="C35" s="4">
         <f>SUM(January:December!C35)</f>
-        <v>925</v>
+        <v>1856</v>
       </c>
       <c r="D35" s="4">
         <f>SUM(January:December!D35)</f>
-        <v>6895</v>
+        <v>13304</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4009,15 +4009,15 @@
       </c>
       <c r="B36" s="3">
         <f>SUM(January:December!B36)</f>
-        <v>799</v>
+        <v>1533</v>
       </c>
       <c r="C36" s="3">
         <f>SUM(January:December!C36)</f>
-        <v>180</v>
+        <v>362</v>
       </c>
       <c r="D36" s="3">
         <f>SUM(January:December!D36)</f>
-        <v>979</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4026,15 +4026,15 @@
       </c>
       <c r="B37" s="4">
         <f>SUM(January:December!B37)</f>
-        <v>2797</v>
+        <v>5555</v>
       </c>
       <c r="C37" s="4">
         <f>SUM(January:December!C37)</f>
-        <v>493</v>
+        <v>1027</v>
       </c>
       <c r="D37" s="4">
         <f>SUM(January:December!D37)</f>
-        <v>3290</v>
+        <v>6582</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4043,15 +4043,15 @@
       </c>
       <c r="B38" s="3">
         <f>SUM(January:December!B38)</f>
-        <v>168</v>
+        <v>328</v>
       </c>
       <c r="C38" s="3">
         <f>SUM(January:December!C38)</f>
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="D38" s="3">
         <f>SUM(January:December!D38)</f>
-        <v>187</v>
+        <v>381</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4060,15 +4060,15 @@
       </c>
       <c r="B39" s="4">
         <f>SUM(January:December!B39)</f>
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="C39" s="4">
         <f>SUM(January:December!C39)</f>
-        <v>240</v>
+        <v>441</v>
       </c>
       <c r="D39" s="4">
         <f>SUM(January:December!D39)</f>
-        <v>345</v>
+        <v>619</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4077,15 +4077,15 @@
       </c>
       <c r="B40" s="7">
         <f>SUM(January:December!B40)</f>
-        <v>430</v>
+        <v>838</v>
       </c>
       <c r="C40" s="7">
         <f>SUM(January:December!C40)</f>
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D40" s="7">
         <f>SUM(January:December!D40)</f>
-        <v>439</v>
+        <v>871</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4094,15 +4094,15 @@
       </c>
       <c r="B41" s="8">
         <f>SUM(January:December!B41)</f>
-        <v>2240</v>
+        <v>4598</v>
       </c>
       <c r="C41" s="8">
         <f>SUM(January:December!C41)</f>
-        <v>87</v>
+        <v>210</v>
       </c>
       <c r="D41" s="8">
         <f>SUM(January:December!D41)</f>
-        <v>2327</v>
+        <v>4808</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4111,15 +4111,15 @@
       </c>
       <c r="B42" s="7">
         <f>SUM(January:December!B42)</f>
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(January:December!C42)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D42" s="7">
         <f>SUM(January:December!D42)</f>
-        <v>53</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4128,15 +4128,15 @@
       </c>
       <c r="B43" s="8">
         <f>SUM(January:December!B43)</f>
-        <v>295</v>
+        <v>619</v>
       </c>
       <c r="C43" s="8">
         <f>SUM(January:December!C43)</f>
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D43" s="8">
         <f>SUM(January:December!D43)</f>
-        <v>310</v>
+        <v>647</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4145,15 +4145,15 @@
       </c>
       <c r="B44" s="3">
         <f>SUM(January:December!B44)</f>
-        <v>260</v>
+        <v>585</v>
       </c>
       <c r="C44" s="3">
         <f>SUM(January:December!C44)</f>
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="D44" s="3">
         <f>SUM(January:December!D44)</f>
-        <v>323</v>
+        <v>710</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4162,15 +4162,15 @@
       </c>
       <c r="B45" s="4">
         <f>SUM(January:December!B45)</f>
-        <v>1296</v>
+        <v>2420</v>
       </c>
       <c r="C45" s="4">
         <f>SUM(January:December!C45)</f>
-        <v>598</v>
+        <v>1095</v>
       </c>
       <c r="D45" s="4">
         <f>SUM(January:December!D45)</f>
-        <v>1894</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4179,15 +4179,15 @@
       </c>
       <c r="B46" s="3">
         <f>SUM(January:December!B46)</f>
-        <v>2449</v>
+        <v>4709</v>
       </c>
       <c r="C46" s="3">
         <f>SUM(January:December!C46)</f>
-        <v>1116</v>
+        <v>1937</v>
       </c>
       <c r="D46" s="3">
         <f>SUM(January:December!D46)</f>
-        <v>3565</v>
+        <v>6646</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4196,15 +4196,15 @@
       </c>
       <c r="B47" s="4">
         <f>SUM(January:December!B47)</f>
-        <v>1149</v>
+        <v>2157</v>
       </c>
       <c r="C47" s="4">
         <f>SUM(January:December!C47)</f>
-        <v>208</v>
+        <v>425</v>
       </c>
       <c r="D47" s="4">
         <f>SUM(January:December!D47)</f>
-        <v>1357</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4213,15 +4213,15 @@
       </c>
       <c r="B48" s="3">
         <f>SUM(January:December!B48)</f>
-        <v>486</v>
+        <v>929</v>
       </c>
       <c r="C48" s="3">
         <f>SUM(January:December!C48)</f>
-        <v>416</v>
+        <v>899</v>
       </c>
       <c r="D48" s="3">
         <f>SUM(January:December!D48)</f>
-        <v>902</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4230,15 +4230,15 @@
       </c>
       <c r="B49" s="4">
         <f>SUM(January:December!B49)</f>
-        <v>3007</v>
+        <v>5966</v>
       </c>
       <c r="C49" s="4">
         <f>SUM(January:December!C49)</f>
-        <v>873</v>
+        <v>1702</v>
       </c>
       <c r="D49" s="4">
         <f>SUM(January:December!D49)</f>
-        <v>3880</v>
+        <v>7668</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4247,15 +4247,15 @@
       </c>
       <c r="B50" s="3">
         <f>SUM(January:December!B50)</f>
-        <v>295</v>
+        <v>575</v>
       </c>
       <c r="C50" s="3">
         <f>SUM(January:December!C50)</f>
-        <v>134</v>
+        <v>239</v>
       </c>
       <c r="D50" s="3">
         <f>SUM(January:December!D50)</f>
-        <v>429</v>
+        <v>814</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4264,15 +4264,15 @@
       </c>
       <c r="B51" s="4">
         <f>SUM(January:December!B51)</f>
-        <v>875</v>
+        <v>1636</v>
       </c>
       <c r="C51" s="4">
         <f>SUM(January:December!C51)</f>
-        <v>695</v>
+        <v>1173</v>
       </c>
       <c r="D51" s="4">
         <f>SUM(January:December!D51)</f>
-        <v>1570</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4281,15 +4281,15 @@
       </c>
       <c r="B52" s="3">
         <f>SUM(January:December!B52)</f>
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="C52" s="3">
         <f>SUM(January:December!C52)</f>
-        <v>64</v>
+        <v>252</v>
       </c>
       <c r="D52" s="3">
         <f>SUM(January:December!D52)</f>
-        <v>143</v>
+        <v>413</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4298,15 +4298,15 @@
       </c>
       <c r="B53" s="4">
         <f>SUM(January:December!B53)</f>
-        <v>180</v>
+        <v>405</v>
       </c>
       <c r="C53" s="4">
         <f>SUM(January:December!C53)</f>
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D53" s="4">
         <f>SUM(January:December!D53)</f>
-        <v>209</v>
+        <v>467</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4315,15 +4315,15 @@
       </c>
       <c r="B54" s="3">
         <f>SUM(January:December!B54)</f>
-        <v>314</v>
+        <v>548</v>
       </c>
       <c r="C54" s="3">
         <f>SUM(January:December!C54)</f>
-        <v>318</v>
+        <v>756</v>
       </c>
       <c r="D54" s="3">
         <f>SUM(January:December!D54)</f>
-        <v>632</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4332,15 +4332,15 @@
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>1021</v>
+        <v>1886</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>272</v>
+        <v>498</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>1293</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4349,15 +4349,15 @@
       </c>
       <c r="B56" s="8">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>3011</v>
+        <v>6147</v>
       </c>
       <c r="C56" s="8">
         <f t="shared" ref="C56:D56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>118</v>
+        <v>283</v>
       </c>
       <c r="D56" s="8">
         <f t="shared" si="1"/>
-        <v>3129</v>
+        <v>6430</v>
       </c>
     </row>
   </sheetData>
@@ -4394,73 +4394,127 @@
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="B2" s="3">
+        <v>3756</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1366</v>
+      </c>
+      <c r="D2" s="3">
+        <v>5122</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="4">
+        <v>2394</v>
+      </c>
+      <c r="C3" s="4">
+        <v>672</v>
+      </c>
+      <c r="D3" s="4">
+        <v>3066</v>
+      </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="B4" s="3">
+        <v>6924</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1140</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8064</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="B5" s="4">
+        <v>84</v>
+      </c>
+      <c r="C5" s="4">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4">
+        <v>102</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="B6" s="3">
+        <v>4684</v>
+      </c>
+      <c r="C6" s="3">
+        <v>966</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5650</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="B7" s="4">
+        <v>728</v>
+      </c>
+      <c r="C7" s="4">
+        <v>169</v>
+      </c>
+      <c r="D7" s="4">
+        <v>897</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="B8" s="3">
+        <v>491</v>
+      </c>
+      <c r="C8" s="3">
+        <v>107</v>
+      </c>
+      <c r="D8" s="3">
+        <v>598</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="B9" s="4">
+        <v>158</v>
+      </c>
+      <c r="C9" s="4">
+        <v>67</v>
+      </c>
+      <c r="D9" s="4">
+        <v>225</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="B10" s="3">
+        <v>41</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3</v>
+      </c>
+      <c r="D10" s="3">
+        <v>44</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -4474,113 +4528,197 @@
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="B12" s="5">
+        <v>16</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="6">
+        <v>73</v>
+      </c>
+      <c r="C13" s="6">
+        <v>52</v>
+      </c>
+      <c r="D13" s="6">
+        <v>125</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="5">
+        <v>596</v>
+      </c>
+      <c r="C14" s="5">
+        <v>126</v>
+      </c>
+      <c r="D14" s="5">
+        <v>722</v>
+      </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="B15" s="6">
+        <v>180</v>
+      </c>
+      <c r="C15" s="6">
+        <v>46</v>
+      </c>
+      <c r="D15" s="6">
+        <v>226</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="B16" s="3">
+        <v>234</v>
+      </c>
+      <c r="C16" s="3">
+        <v>60</v>
+      </c>
+      <c r="D16" s="3">
+        <v>294</v>
+      </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="B17" s="4">
+        <v>1070</v>
+      </c>
+      <c r="C17" s="4">
+        <v>728</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1798</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="B18" s="3">
+        <v>91</v>
+      </c>
+      <c r="C18" s="3">
+        <v>114</v>
+      </c>
+      <c r="D18" s="3">
+        <v>205</v>
+      </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
+      <c r="B19" s="4">
+        <v>1622</v>
+      </c>
+      <c r="C19" s="4">
+        <v>724</v>
+      </c>
+      <c r="D19" s="4">
+        <v>2346</v>
+      </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="B20" s="3">
+        <v>28</v>
+      </c>
+      <c r="C20" s="3">
+        <v>4</v>
+      </c>
+      <c r="D20" s="3">
+        <v>32</v>
+      </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
+      <c r="B21" s="4">
+        <v>1349</v>
+      </c>
+      <c r="C21" s="4">
+        <v>448</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1797</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="B22" s="3">
+        <v>199</v>
+      </c>
+      <c r="C22" s="3">
+        <v>129</v>
+      </c>
+      <c r="D22" s="3">
+        <v>328</v>
+      </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="B23" s="4">
+        <v>1932</v>
+      </c>
+      <c r="C23" s="4">
+        <v>581</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2513</v>
+      </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="B24" s="3">
+        <v>9089</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1901</v>
+      </c>
+      <c r="D24" s="3">
+        <v>10990</v>
+      </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
+      <c r="B25" s="4">
+        <v>391</v>
+      </c>
+      <c r="C25" s="4">
+        <v>174</v>
+      </c>
+      <c r="D25" s="4">
+        <v>565</v>
+      </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
@@ -4594,225 +4732,393 @@
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
+      <c r="B27" s="4">
+        <v>351</v>
+      </c>
+      <c r="C27" s="4">
+        <v>172</v>
+      </c>
+      <c r="D27" s="4">
+        <v>523</v>
+      </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="B28" s="3">
+        <v>316</v>
+      </c>
+      <c r="C28" s="3">
+        <v>126</v>
+      </c>
+      <c r="D28" s="3">
+        <v>442</v>
+      </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="B29" s="4">
+        <v>1506</v>
+      </c>
+      <c r="C29" s="4">
+        <v>870</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2376</v>
+      </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="B30" s="3">
+        <v>21</v>
+      </c>
+      <c r="C30" s="3">
+        <v>9</v>
+      </c>
+      <c r="D30" s="3">
+        <v>30</v>
+      </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+      <c r="B31" s="4">
+        <v>332</v>
+      </c>
+      <c r="C31" s="4">
+        <v>139</v>
+      </c>
+      <c r="D31" s="4">
+        <v>471</v>
+      </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="B32" s="3">
+        <v>1118</v>
+      </c>
+      <c r="C32" s="3">
+        <v>399</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1517</v>
+      </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="B33" s="4">
+        <v>757</v>
+      </c>
+      <c r="C33" s="4">
+        <v>384</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1141</v>
+      </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
+      <c r="B34" s="3">
+        <v>591</v>
+      </c>
+      <c r="C34" s="3">
+        <v>224</v>
+      </c>
+      <c r="D34" s="3">
+        <v>815</v>
+      </c>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
+      <c r="B35" s="4">
+        <v>5478</v>
+      </c>
+      <c r="C35" s="4">
+        <v>931</v>
+      </c>
+      <c r="D35" s="4">
+        <v>6409</v>
+      </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="B36" s="3">
+        <v>734</v>
+      </c>
+      <c r="C36" s="3">
+        <v>182</v>
+      </c>
+      <c r="D36" s="3">
+        <v>916</v>
+      </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
+      <c r="B37" s="4">
+        <v>2758</v>
+      </c>
+      <c r="C37" s="4">
+        <v>534</v>
+      </c>
+      <c r="D37" s="4">
+        <v>3292</v>
+      </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
+      <c r="B38" s="3">
+        <v>160</v>
+      </c>
+      <c r="C38" s="3">
+        <v>34</v>
+      </c>
+      <c r="D38" s="3">
+        <v>194</v>
+      </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
+      <c r="B39" s="4">
+        <v>73</v>
+      </c>
+      <c r="C39" s="4">
+        <v>201</v>
+      </c>
+      <c r="D39" s="4">
+        <v>274</v>
+      </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+      <c r="B40" s="7">
+        <v>408</v>
+      </c>
+      <c r="C40" s="7">
+        <v>24</v>
+      </c>
+      <c r="D40" s="7">
+        <v>432</v>
+      </c>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="B41" s="8">
+        <v>2358</v>
+      </c>
+      <c r="C41" s="8">
+        <v>123</v>
+      </c>
+      <c r="D41" s="8">
+        <v>2481</v>
+      </c>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
+      <c r="B42" s="7">
+        <v>46</v>
+      </c>
+      <c r="C42" s="7">
+        <v>5</v>
+      </c>
+      <c r="D42" s="7">
+        <v>51</v>
+      </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
+      <c r="B43" s="8">
+        <v>324</v>
+      </c>
+      <c r="C43" s="8">
+        <v>13</v>
+      </c>
+      <c r="D43" s="8">
+        <v>337</v>
+      </c>
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
+      <c r="B44" s="3">
+        <v>325</v>
+      </c>
+      <c r="C44" s="3">
+        <v>62</v>
+      </c>
+      <c r="D44" s="3">
+        <v>387</v>
+      </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
+      <c r="B45" s="4">
+        <v>1124</v>
+      </c>
+      <c r="C45" s="4">
+        <v>497</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1621</v>
+      </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
+      <c r="B46" s="3">
+        <v>2260</v>
+      </c>
+      <c r="C46" s="3">
+        <v>821</v>
+      </c>
+      <c r="D46" s="3">
+        <v>3081</v>
+      </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
+      <c r="B47" s="4">
+        <v>1008</v>
+      </c>
+      <c r="C47" s="4">
+        <v>217</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1225</v>
+      </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
+      <c r="B48" s="3">
+        <v>443</v>
+      </c>
+      <c r="C48" s="3">
+        <v>483</v>
+      </c>
+      <c r="D48" s="3">
+        <v>926</v>
+      </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
+      <c r="B49" s="4">
+        <v>2959</v>
+      </c>
+      <c r="C49" s="4">
+        <v>829</v>
+      </c>
+      <c r="D49" s="4">
+        <v>3788</v>
+      </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
+      <c r="B50" s="3">
+        <v>280</v>
+      </c>
+      <c r="C50" s="3">
+        <v>105</v>
+      </c>
+      <c r="D50" s="3">
+        <v>385</v>
+      </c>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
+      <c r="B51" s="4">
+        <v>761</v>
+      </c>
+      <c r="C51" s="4">
+        <v>478</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1239</v>
+      </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
+      <c r="B52" s="3">
+        <v>82</v>
+      </c>
+      <c r="C52" s="3">
+        <v>188</v>
+      </c>
+      <c r="D52" s="3">
+        <v>270</v>
+      </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
+      <c r="B53" s="4">
+        <v>225</v>
+      </c>
+      <c r="C53" s="4">
+        <v>33</v>
+      </c>
+      <c r="D53" s="4">
+        <v>258</v>
+      </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
+      <c r="B54" s="3">
+        <v>234</v>
+      </c>
+      <c r="C54" s="3">
+        <v>438</v>
+      </c>
+      <c r="D54" s="3">
+        <v>672</v>
+      </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
@@ -4820,15 +5126,15 @@
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>0</v>
+        <v>865</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4837,15 +5143,15 @@
       </c>
       <c r="B56" s="8">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>0</v>
+        <v>3136</v>
       </c>
       <c r="C56" s="8">
         <f t="shared" ref="C56:D56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="D56" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3301</v>
       </c>
     </row>
   </sheetData>

--- a/statistics_files/2026/2026_99_gc_sharing.xlsx
+++ b/statistics_files/2026/2026_99_gc_sharing.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Staff\Documents\GitHub\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41656763-E07E-4ACE-BE34-0C5981AF8371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F118B7-5011-4BBC-BF7B-22F5DDE96F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -1149,13 +1149,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>5663</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>3255</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>9155</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -1301,7 +1301,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>2530</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>11305</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -1505,7 +1505,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>2580</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>6895</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>3290</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>3565</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>3880</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -1941,13 +1941,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1969,7 +1969,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1977,7 +1977,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -1985,7 +1985,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1993,7 +1993,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -2001,7 +2001,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -2009,7 +2009,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -2017,7 +2017,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -2025,7 +2025,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -2033,7 +2033,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -2041,7 +2041,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -2049,7 +2049,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -2057,7 +2057,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -2065,7 +2065,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -2073,7 +2073,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -2081,7 +2081,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -2089,7 +2089,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -2097,7 +2097,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -2105,7 +2105,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -2113,7 +2113,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -2121,7 +2121,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -2129,7 +2129,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -2137,7 +2137,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -2145,7 +2145,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -2153,7 +2153,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -2161,7 +2161,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -2169,7 +2169,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -2177,7 +2177,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -2185,7 +2185,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -2193,7 +2193,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -2201,7 +2201,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -2209,7 +2209,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -2217,7 +2217,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -2225,7 +2225,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -2233,7 +2233,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -2241,7 +2241,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -2249,7 +2249,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -2257,7 +2257,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -2265,7 +2265,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -2273,7 +2273,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -2281,7 +2281,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -2289,7 +2289,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -2297,7 +2297,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -2305,7 +2305,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -2313,7 +2313,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -2321,7 +2321,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -2329,7 +2329,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -2337,7 +2337,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -2345,7 +2345,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -2353,7 +2353,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -2361,7 +2361,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -2369,7 +2369,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -2385,7 +2385,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -2429,13 +2429,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2457,7 +2457,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -2465,7 +2465,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -2473,7 +2473,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2481,7 +2481,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -2489,7 +2489,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -2497,7 +2497,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -2505,7 +2505,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -2513,7 +2513,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -2521,7 +2521,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -2529,7 +2529,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -2537,7 +2537,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -2545,7 +2545,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -2553,7 +2553,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -2561,7 +2561,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -2569,7 +2569,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -2577,7 +2577,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -2585,7 +2585,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -2593,7 +2593,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -2601,7 +2601,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -2609,7 +2609,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -2617,7 +2617,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -2625,7 +2625,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -2633,7 +2633,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -2641,7 +2641,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -2649,7 +2649,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -2657,7 +2657,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -2665,7 +2665,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -2673,7 +2673,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -2681,7 +2681,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -2689,7 +2689,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -2697,7 +2697,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -2705,7 +2705,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -2713,7 +2713,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -2721,7 +2721,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -2729,7 +2729,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -2737,7 +2737,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -2745,7 +2745,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -2753,7 +2753,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -2761,7 +2761,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -2769,7 +2769,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -2777,7 +2777,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -2785,7 +2785,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -2793,7 +2793,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -2801,7 +2801,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -2809,7 +2809,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -2817,7 +2817,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -2825,7 +2825,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -2833,7 +2833,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -2841,7 +2841,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -2849,7 +2849,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -2857,7 +2857,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -2865,7 +2865,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -2873,7 +2873,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -2917,13 +2917,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2945,7 +2945,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -2953,7 +2953,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -2961,7 +2961,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2969,7 +2969,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -2977,7 +2977,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -2985,7 +2985,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -2993,7 +2993,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -3001,7 +3001,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -3009,7 +3009,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -3017,7 +3017,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -3025,7 +3025,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -3033,7 +3033,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -3041,7 +3041,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -3049,7 +3049,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -3057,7 +3057,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -3065,7 +3065,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -3073,7 +3073,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -3081,7 +3081,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -3089,7 +3089,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -3097,7 +3097,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -3105,7 +3105,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -3113,7 +3113,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -3121,7 +3121,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -3129,7 +3129,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -3137,7 +3137,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -3145,7 +3145,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -3153,7 +3153,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -3161,7 +3161,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -3169,7 +3169,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -3177,7 +3177,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -3185,7 +3185,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -3193,7 +3193,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -3201,7 +3201,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -3209,7 +3209,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -3217,7 +3217,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -3225,7 +3225,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -3233,7 +3233,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -3241,7 +3241,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -3249,7 +3249,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -3257,7 +3257,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -3265,7 +3265,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -3273,7 +3273,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -3281,7 +3281,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -3289,7 +3289,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -3297,7 +3297,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -3305,7 +3305,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -3313,7 +3313,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -3321,7 +3321,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -3329,7 +3329,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -3337,7 +3337,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -3345,7 +3345,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -3353,7 +3353,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -3361,7 +3361,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -3405,13 +3405,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3425,149 +3425,149 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3">
         <f>SUM(January:December!B2)</f>
-        <v>7978</v>
+        <v>12222</v>
       </c>
       <c r="C2" s="3">
         <f>SUM(January:December!C2)</f>
-        <v>2807</v>
+        <v>4403</v>
       </c>
       <c r="D2" s="3">
         <f>SUM(January:December!D2)</f>
-        <v>10785</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16625</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="4">
         <f>SUM(January:December!B3)</f>
-        <v>4978</v>
+        <v>7731</v>
       </c>
       <c r="C3" s="4">
         <f>SUM(January:December!C3)</f>
-        <v>1343</v>
+        <v>1993</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(January:December!D3)</f>
-        <v>6321</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9724</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="3">
         <f>SUM(January:December!B4)</f>
-        <v>14710</v>
+        <v>22884</v>
       </c>
       <c r="C4" s="3">
         <f>SUM(January:December!C4)</f>
-        <v>2509</v>
+        <v>3822</v>
       </c>
       <c r="D4" s="3">
         <f>SUM(January:December!D4)</f>
-        <v>17219</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26706</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>SUM(January:December!B5)</f>
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="C5" s="4">
         <f>SUM(January:December!C5)</f>
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D5" s="4">
         <f>SUM(January:December!D5)</f>
-        <v>191</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="3">
         <f>SUM(January:December!B6)</f>
-        <v>9794</v>
+        <v>15023</v>
       </c>
       <c r="C6" s="3">
         <f>SUM(January:December!C6)</f>
-        <v>2128</v>
+        <v>3189</v>
       </c>
       <c r="D6" s="3">
         <f>SUM(January:December!D6)</f>
-        <v>11922</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>18212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>SUM(January:December!B7)</f>
-        <v>1573</v>
+        <v>2054</v>
       </c>
       <c r="C7" s="4">
         <f>SUM(January:December!C7)</f>
-        <v>386</v>
+        <v>614</v>
       </c>
       <c r="D7" s="4">
         <f>SUM(January:December!D7)</f>
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="3">
         <f>SUM(January:December!B8)</f>
-        <v>865</v>
+        <v>1276</v>
       </c>
       <c r="C8" s="3">
         <f>SUM(January:December!C8)</f>
-        <v>218</v>
+        <v>362</v>
       </c>
       <c r="D8" s="3">
         <f>SUM(January:December!D8)</f>
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>SUM(January:December!B9)</f>
-        <v>336</v>
+        <v>517</v>
       </c>
       <c r="C9" s="4">
         <f>SUM(January:December!C9)</f>
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="D9" s="4">
         <f>SUM(January:December!D9)</f>
-        <v>476</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="3">
         <f>SUM(January:December!B10)</f>
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="C10" s="3">
         <f>SUM(January:December!C10)</f>
@@ -3575,10 +3575,10 @@
       </c>
       <c r="D10" s="3">
         <f>SUM(January:December!D10)</f>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -3595,149 +3595,149 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="5">
         <f>SUM(January:December!B12)</f>
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C12" s="5">
         <f>SUM(January:December!C12)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D12" s="5">
         <f>SUM(January:December!D12)</f>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="6">
         <f>SUM(January:December!B13)</f>
-        <v>181</v>
+        <v>326</v>
       </c>
       <c r="C13" s="6">
         <f>SUM(January:December!C13)</f>
-        <v>94</v>
+        <v>163</v>
       </c>
       <c r="D13" s="6">
         <f>SUM(January:December!D13)</f>
-        <v>275</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>1173</v>
+        <v>1845</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>294</v>
+        <v>431</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>1467</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="6">
         <f>SUM(January:December!B15)</f>
-        <v>495</v>
+        <v>772</v>
       </c>
       <c r="C15" s="6">
         <f>SUM(January:December!C15)</f>
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="D15" s="6">
         <f>SUM(January:December!D15)</f>
-        <v>596</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B16" s="3">
         <f>SUM(January:December!B16)</f>
-        <v>406</v>
+        <v>657</v>
       </c>
       <c r="C16" s="3">
         <f>SUM(January:December!C16)</f>
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="D16" s="3">
         <f>SUM(January:December!D16)</f>
-        <v>540</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>SUM(January:December!B17)</f>
-        <v>2274</v>
+        <v>3612</v>
       </c>
       <c r="C17" s="4">
         <f>SUM(January:December!C17)</f>
-        <v>1422</v>
+        <v>2118</v>
       </c>
       <c r="D17" s="4">
         <f>SUM(January:December!D17)</f>
-        <v>3696</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5730</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
         <f>SUM(January:December!B18)</f>
-        <v>181</v>
+        <v>285</v>
       </c>
       <c r="C18" s="3">
         <f>SUM(January:December!C18)</f>
-        <v>203</v>
+        <v>276</v>
       </c>
       <c r="D18" s="3">
         <f>SUM(January:December!D18)</f>
-        <v>384</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>SUM(January:December!B19)</f>
-        <v>3169</v>
+        <v>4622</v>
       </c>
       <c r="C19" s="4">
         <f>SUM(January:December!C19)</f>
-        <v>1209</v>
+        <v>1789</v>
       </c>
       <c r="D19" s="4">
         <f>SUM(January:December!D19)</f>
-        <v>4378</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6411</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="3">
         <f>SUM(January:December!B20)</f>
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="C20" s="3">
         <f>SUM(January:December!C20)</f>
@@ -3745,95 +3745,95 @@
       </c>
       <c r="D20" s="3">
         <f>SUM(January:December!D20)</f>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="4">
         <f>SUM(January:December!B21)</f>
-        <v>2866</v>
+        <v>4457</v>
       </c>
       <c r="C21" s="4">
         <f>SUM(January:December!C21)</f>
-        <v>949</v>
+        <v>1512</v>
       </c>
       <c r="D21" s="4">
         <f>SUM(January:December!D21)</f>
-        <v>3815</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5969</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="3">
         <f>SUM(January:December!B22)</f>
-        <v>422</v>
+        <v>690</v>
       </c>
       <c r="C22" s="3">
         <f>SUM(January:December!C22)</f>
-        <v>219</v>
+        <v>287</v>
       </c>
       <c r="D22" s="3">
         <f>SUM(January:December!D22)</f>
-        <v>641</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="4">
         <f>SUM(January:December!B23)</f>
-        <v>3849</v>
+        <v>6222</v>
       </c>
       <c r="C23" s="4">
         <f>SUM(January:December!C23)</f>
-        <v>1194</v>
+        <v>2054</v>
       </c>
       <c r="D23" s="4">
         <f>SUM(January:December!D23)</f>
-        <v>5043</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8276</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B24" s="3">
         <f>SUM(January:December!B24)</f>
-        <v>18585</v>
+        <v>28888</v>
       </c>
       <c r="C24" s="3">
         <f>SUM(January:December!C24)</f>
-        <v>3710</v>
+        <v>5484</v>
       </c>
       <c r="D24" s="3">
         <f>SUM(January:December!D24)</f>
-        <v>22295</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34372</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="4">
         <f>SUM(January:December!B25)</f>
-        <v>797</v>
+        <v>1217</v>
       </c>
       <c r="C25" s="4">
         <f>SUM(January:December!C25)</f>
-        <v>346</v>
+        <v>463</v>
       </c>
       <c r="D25" s="4">
         <f>SUM(January:December!D25)</f>
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -3850,514 +3850,514 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="4">
         <f>SUM(January:December!B27)</f>
-        <v>761</v>
+        <v>1211</v>
       </c>
       <c r="C27" s="4">
         <f>SUM(January:December!C27)</f>
-        <v>403</v>
+        <v>572</v>
       </c>
       <c r="D27" s="4">
         <f>SUM(January:December!D27)</f>
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B28" s="3">
         <f>SUM(January:December!B28)</f>
-        <v>643</v>
+        <v>959</v>
       </c>
       <c r="C28" s="3">
         <f>SUM(January:December!C28)</f>
-        <v>258</v>
+        <v>411</v>
       </c>
       <c r="D28" s="3">
         <f>SUM(January:December!D28)</f>
-        <v>901</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B29" s="4">
         <f>SUM(January:December!B29)</f>
-        <v>3195</v>
+        <v>4943</v>
       </c>
       <c r="C29" s="4">
         <f>SUM(January:December!C29)</f>
-        <v>1761</v>
+        <v>2561</v>
       </c>
       <c r="D29" s="4">
         <f>SUM(January:December!D29)</f>
-        <v>4956</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7504</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B30" s="3">
         <f>SUM(January:December!B30)</f>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C30" s="3">
         <f>SUM(January:December!C30)</f>
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D30" s="3">
         <f>SUM(January:December!D30)</f>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B31" s="4">
         <f>SUM(January:December!B31)</f>
-        <v>707</v>
+        <v>1042</v>
       </c>
       <c r="C31" s="4">
         <f>SUM(January:December!C31)</f>
-        <v>258</v>
+        <v>404</v>
       </c>
       <c r="D31" s="4">
         <f>SUM(January:December!D31)</f>
-        <v>965</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B32" s="3">
         <f>SUM(January:December!B32)</f>
-        <v>2387</v>
+        <v>3604</v>
       </c>
       <c r="C32" s="3">
         <f>SUM(January:December!C32)</f>
-        <v>920</v>
+        <v>1349</v>
       </c>
       <c r="D32" s="3">
         <f>SUM(January:December!D32)</f>
-        <v>3307</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4953</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B33" s="4">
         <f>SUM(January:December!B33)</f>
-        <v>1445</v>
+        <v>2251</v>
       </c>
       <c r="C33" s="4">
         <f>SUM(January:December!C33)</f>
-        <v>757</v>
+        <v>1143</v>
       </c>
       <c r="D33" s="4">
         <f>SUM(January:December!D33)</f>
-        <v>2202</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3394</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B34" s="3">
         <f>SUM(January:December!B34)</f>
-        <v>1028</v>
+        <v>1367</v>
       </c>
       <c r="C34" s="3">
         <f>SUM(January:December!C34)</f>
-        <v>432</v>
+        <v>581</v>
       </c>
       <c r="D34" s="3">
         <f>SUM(January:December!D34)</f>
-        <v>1460</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B35" s="4">
         <f>SUM(January:December!B35)</f>
-        <v>11448</v>
+        <v>16465</v>
       </c>
       <c r="C35" s="4">
         <f>SUM(January:December!C35)</f>
-        <v>1856</v>
+        <v>2915</v>
       </c>
       <c r="D35" s="4">
         <f>SUM(January:December!D35)</f>
-        <v>13304</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19380</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B36" s="3">
         <f>SUM(January:December!B36)</f>
-        <v>1533</v>
+        <v>2255</v>
       </c>
       <c r="C36" s="3">
         <f>SUM(January:December!C36)</f>
-        <v>362</v>
+        <v>515</v>
       </c>
       <c r="D36" s="3">
         <f>SUM(January:December!D36)</f>
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2770</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B37" s="4">
         <f>SUM(January:December!B37)</f>
-        <v>5555</v>
+        <v>8727</v>
       </c>
       <c r="C37" s="4">
         <f>SUM(January:December!C37)</f>
-        <v>1027</v>
+        <v>1709</v>
       </c>
       <c r="D37" s="4">
         <f>SUM(January:December!D37)</f>
-        <v>6582</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10436</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B38" s="3">
         <f>SUM(January:December!B38)</f>
-        <v>328</v>
+        <v>528</v>
       </c>
       <c r="C38" s="3">
         <f>SUM(January:December!C38)</f>
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="D38" s="3">
         <f>SUM(January:December!D38)</f>
-        <v>381</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B39" s="4">
         <f>SUM(January:December!B39)</f>
-        <v>178</v>
+        <v>299</v>
       </c>
       <c r="C39" s="4">
         <f>SUM(January:December!C39)</f>
-        <v>441</v>
+        <v>558</v>
       </c>
       <c r="D39" s="4">
         <f>SUM(January:December!D39)</f>
-        <v>619</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B40" s="7">
         <f>SUM(January:December!B40)</f>
-        <v>838</v>
+        <v>1283</v>
       </c>
       <c r="C40" s="7">
         <f>SUM(January:December!C40)</f>
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="D40" s="7">
         <f>SUM(January:December!D40)</f>
-        <v>871</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
       <c r="B41" s="8">
         <f>SUM(January:December!B41)</f>
-        <v>4598</v>
+        <v>6596</v>
       </c>
       <c r="C41" s="8">
         <f>SUM(January:December!C41)</f>
-        <v>210</v>
+        <v>347</v>
       </c>
       <c r="D41" s="8">
         <f>SUM(January:December!D41)</f>
-        <v>4808</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6943</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B42" s="7">
         <f>SUM(January:December!B42)</f>
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(January:December!C42)</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D42" s="7">
         <f>SUM(January:December!D42)</f>
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B43" s="8">
         <f>SUM(January:December!B43)</f>
-        <v>619</v>
+        <v>861</v>
       </c>
       <c r="C43" s="8">
         <f>SUM(January:December!C43)</f>
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D43" s="8">
         <f>SUM(January:December!D43)</f>
-        <v>647</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B44" s="3">
         <f>SUM(January:December!B44)</f>
-        <v>585</v>
+        <v>945</v>
       </c>
       <c r="C44" s="3">
         <f>SUM(January:December!C44)</f>
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="D44" s="3">
         <f>SUM(January:December!D44)</f>
-        <v>710</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
       <c r="B45" s="4">
         <f>SUM(January:December!B45)</f>
-        <v>2420</v>
+        <v>3746</v>
       </c>
       <c r="C45" s="4">
         <f>SUM(January:December!C45)</f>
-        <v>1095</v>
+        <v>1629</v>
       </c>
       <c r="D45" s="4">
         <f>SUM(January:December!D45)</f>
-        <v>3515</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B46" s="3">
         <f>SUM(January:December!B46)</f>
-        <v>4709</v>
+        <v>7275</v>
       </c>
       <c r="C46" s="3">
         <f>SUM(January:December!C46)</f>
-        <v>1937</v>
+        <v>2910</v>
       </c>
       <c r="D46" s="3">
         <f>SUM(January:December!D46)</f>
-        <v>6646</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10185</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B47" s="4">
         <f>SUM(January:December!B47)</f>
-        <v>2157</v>
+        <v>3440</v>
       </c>
       <c r="C47" s="4">
         <f>SUM(January:December!C47)</f>
-        <v>425</v>
+        <v>720</v>
       </c>
       <c r="D47" s="4">
         <f>SUM(January:December!D47)</f>
-        <v>2582</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B48" s="3">
         <f>SUM(January:December!B48)</f>
-        <v>929</v>
+        <v>1455</v>
       </c>
       <c r="C48" s="3">
         <f>SUM(January:December!C48)</f>
-        <v>899</v>
+        <v>1456</v>
       </c>
       <c r="D48" s="3">
         <f>SUM(January:December!D48)</f>
-        <v>1828</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2911</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B49" s="4">
         <f>SUM(January:December!B49)</f>
-        <v>5966</v>
+        <v>9015</v>
       </c>
       <c r="C49" s="4">
         <f>SUM(January:December!C49)</f>
-        <v>1702</v>
+        <v>2751</v>
       </c>
       <c r="D49" s="4">
         <f>SUM(January:December!D49)</f>
-        <v>7668</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11766</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B50" s="3">
         <f>SUM(January:December!B50)</f>
-        <v>575</v>
+        <v>952</v>
       </c>
       <c r="C50" s="3">
         <f>SUM(January:December!C50)</f>
-        <v>239</v>
+        <v>382</v>
       </c>
       <c r="D50" s="3">
         <f>SUM(January:December!D50)</f>
-        <v>814</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B51" s="4">
         <f>SUM(January:December!B51)</f>
-        <v>1636</v>
+        <v>2587</v>
       </c>
       <c r="C51" s="4">
         <f>SUM(January:December!C51)</f>
-        <v>1173</v>
+        <v>1672</v>
       </c>
       <c r="D51" s="4">
         <f>SUM(January:December!D51)</f>
-        <v>2809</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4259</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B52" s="3">
         <f>SUM(January:December!B52)</f>
-        <v>161</v>
+        <v>236</v>
       </c>
       <c r="C52" s="3">
         <f>SUM(January:December!C52)</f>
-        <v>252</v>
+        <v>413</v>
       </c>
       <c r="D52" s="3">
         <f>SUM(January:December!D52)</f>
-        <v>413</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
       <c r="B53" s="4">
         <f>SUM(January:December!B53)</f>
-        <v>405</v>
+        <v>591</v>
       </c>
       <c r="C53" s="4">
         <f>SUM(January:December!C53)</f>
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D53" s="4">
         <f>SUM(January:December!D53)</f>
-        <v>467</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B54" s="3">
         <f>SUM(January:December!B54)</f>
-        <v>548</v>
+        <v>826</v>
       </c>
       <c r="C54" s="3">
         <f>SUM(January:December!C54)</f>
-        <v>756</v>
+        <v>1204</v>
       </c>
       <c r="D54" s="3">
         <f>SUM(January:December!D54)</f>
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>1886</v>
+        <v>2993</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>498</v>
+        <v>758</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>2384</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3751</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B56" s="8">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>6147</v>
+        <v>8867</v>
       </c>
       <c r="C56" s="8">
         <f t="shared" ref="C56:D56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>283</v>
+        <v>466</v>
       </c>
       <c r="D56" s="8">
         <f t="shared" si="1"/>
-        <v>6430</v>
+        <v>9333</v>
       </c>
     </row>
   </sheetData>
@@ -4370,13 +4370,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>5122</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>3066</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>8064</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>5650</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -4524,7 +4524,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>10990</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -4728,7 +4728,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>2376</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>6409</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -4882,7 +4882,7 @@
         <v>3292</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -4896,7 +4896,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -4924,7 +4924,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>3081</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>3788</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -5106,7 +5106,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -5164,13 +5164,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5184,79 +5184,131 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="3">
+        <v>4244</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1596</v>
+      </c>
+      <c r="D2" s="3">
+        <v>5840</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>2753</v>
+      </c>
+      <c r="C3" s="4">
+        <v>650</v>
+      </c>
+      <c r="D3" s="4">
+        <v>3403</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="3">
+        <v>8174</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1313</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9487</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
+        <v>75</v>
+      </c>
+      <c r="C5" s="4">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
+        <v>5229</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1061</v>
+      </c>
+      <c r="D6" s="3">
+        <v>6290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
+        <v>481</v>
+      </c>
+      <c r="C7" s="4">
+        <v>228</v>
+      </c>
+      <c r="D7" s="4">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3">
+        <v>411</v>
+      </c>
+      <c r="C8" s="3">
+        <v>144</v>
+      </c>
+      <c r="D8" s="3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>181</v>
+      </c>
+      <c r="C9" s="4">
+        <v>45</v>
+      </c>
+      <c r="D9" s="4">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="3">
+        <v>46</v>
+      </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D10" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -5264,119 +5316,201 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="5">
+        <v>13</v>
+      </c>
+      <c r="C12" s="5">
+        <v>3</v>
+      </c>
+      <c r="D12" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="6">
+        <v>145</v>
+      </c>
+      <c r="C13" s="6">
+        <v>69</v>
+      </c>
+      <c r="D13" s="6">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
+        <v>672</v>
+      </c>
+      <c r="C14" s="5">
+        <v>137</v>
+      </c>
+      <c r="D14" s="5">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="6">
+        <v>277</v>
+      </c>
+      <c r="C15" s="6">
+        <v>51</v>
+      </c>
+      <c r="D15" s="6">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3">
+        <v>251</v>
+      </c>
+      <c r="C16" s="3">
+        <v>53</v>
+      </c>
+      <c r="D16" s="3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="4">
+        <v>1338</v>
+      </c>
+      <c r="C17" s="4">
+        <v>696</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="3">
+        <v>104</v>
+      </c>
+      <c r="C18" s="3">
+        <v>73</v>
+      </c>
+      <c r="D18" s="3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="4">
+        <v>1453</v>
+      </c>
+      <c r="C19" s="4">
+        <v>580</v>
+      </c>
+      <c r="D19" s="4">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3"/>
+      <c r="B20" s="3">
+        <v>39</v>
+      </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D20" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="4">
+        <v>1591</v>
+      </c>
+      <c r="C21" s="4">
+        <v>563</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="3">
+        <v>268</v>
+      </c>
+      <c r="C22" s="3">
+        <v>68</v>
+      </c>
+      <c r="D22" s="3">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="4">
+        <v>2373</v>
+      </c>
+      <c r="C23" s="4">
+        <v>860</v>
+      </c>
+      <c r="D23" s="4">
+        <v>3233</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="3">
+        <v>10303</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1774</v>
+      </c>
+      <c r="D24" s="3">
+        <v>12077</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="4">
+        <v>420</v>
+      </c>
+      <c r="C25" s="4">
+        <v>117</v>
+      </c>
+      <c r="D25" s="4">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -5384,262 +5518,430 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="4">
+        <v>450</v>
+      </c>
+      <c r="C27" s="4">
+        <v>169</v>
+      </c>
+      <c r="D27" s="4">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="3">
+        <v>316</v>
+      </c>
+      <c r="C28" s="3">
+        <v>153</v>
+      </c>
+      <c r="D28" s="3">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="4">
+        <v>1748</v>
+      </c>
+      <c r="C29" s="4">
+        <v>800</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="3">
+        <v>4</v>
+      </c>
+      <c r="C30" s="3">
+        <v>27</v>
+      </c>
+      <c r="D30" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="4">
+        <v>335</v>
+      </c>
+      <c r="C31" s="4">
+        <v>146</v>
+      </c>
+      <c r="D31" s="4">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="3">
+        <v>1217</v>
+      </c>
+      <c r="C32" s="3">
+        <v>429</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="4">
+        <v>806</v>
+      </c>
+      <c r="C33" s="4">
+        <v>386</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-    </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="3">
+        <v>339</v>
+      </c>
+      <c r="C34" s="3">
+        <v>149</v>
+      </c>
+      <c r="D34" s="3">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="4">
+        <v>5017</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1059</v>
+      </c>
+      <c r="D35" s="4">
+        <v>6076</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-    </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="3">
+        <v>722</v>
+      </c>
+      <c r="C36" s="3">
+        <v>153</v>
+      </c>
+      <c r="D36" s="3">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-    </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="4">
+        <v>3172</v>
+      </c>
+      <c r="C37" s="4">
+        <v>682</v>
+      </c>
+      <c r="D37" s="4">
+        <v>3854</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-    </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="3">
+        <v>200</v>
+      </c>
+      <c r="C38" s="3">
+        <v>33</v>
+      </c>
+      <c r="D38" s="3">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-    </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="4">
+        <v>121</v>
+      </c>
+      <c r="C39" s="4">
+        <v>117</v>
+      </c>
+      <c r="D39" s="4">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-    </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="7">
+        <v>445</v>
+      </c>
+      <c r="C40" s="7">
+        <v>31</v>
+      </c>
+      <c r="D40" s="7">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="8">
+        <v>1998</v>
+      </c>
+      <c r="C41" s="8">
+        <v>137</v>
+      </c>
+      <c r="D41" s="8">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-    </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="7">
+        <v>35</v>
+      </c>
+      <c r="C42" s="7">
+        <v>6</v>
+      </c>
+      <c r="D42" s="7">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="8">
+        <v>242</v>
+      </c>
+      <c r="C43" s="8">
+        <v>9</v>
+      </c>
+      <c r="D43" s="8">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-    </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="3">
+        <v>360</v>
+      </c>
+      <c r="C44" s="3">
+        <v>51</v>
+      </c>
+      <c r="D44" s="3">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="4">
+        <v>1326</v>
+      </c>
+      <c r="C45" s="4">
+        <v>534</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="3">
+        <v>2566</v>
+      </c>
+      <c r="C46" s="3">
+        <v>973</v>
+      </c>
+      <c r="D46" s="3">
+        <v>3539</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="4">
+        <v>1283</v>
+      </c>
+      <c r="C47" s="4">
+        <v>295</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-    </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="3">
+        <v>526</v>
+      </c>
+      <c r="C48" s="3">
+        <v>557</v>
+      </c>
+      <c r="D48" s="3">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-    </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="4">
+        <v>3049</v>
+      </c>
+      <c r="C49" s="4">
+        <v>1049</v>
+      </c>
+      <c r="D49" s="4">
+        <v>4098</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-    </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="3">
+        <v>377</v>
+      </c>
+      <c r="C50" s="3">
+        <v>143</v>
+      </c>
+      <c r="D50" s="3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-    </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="4">
+        <v>951</v>
+      </c>
+      <c r="C51" s="4">
+        <v>499</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-    </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="3">
+        <v>75</v>
+      </c>
+      <c r="C52" s="3">
+        <v>161</v>
+      </c>
+      <c r="D52" s="3">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-    </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="4">
+        <v>186</v>
+      </c>
+      <c r="C53" s="4">
+        <v>20</v>
+      </c>
+      <c r="D53" s="4">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-    </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="3">
+        <v>278</v>
+      </c>
+      <c r="C54" s="3">
+        <v>448</v>
+      </c>
+      <c r="D54" s="3">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>0</v>
+        <v>1107</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B56" s="8">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>0</v>
+        <v>2720</v>
       </c>
       <c r="C56" s="8">
         <f t="shared" ref="C56:D56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="D56" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2903</v>
       </c>
     </row>
   </sheetData>
@@ -5652,13 +5954,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5672,7 +5974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -5680,7 +5982,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -5688,7 +5990,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -5696,7 +5998,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -5704,7 +6006,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -5712,7 +6014,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -5720,7 +6022,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -5728,7 +6030,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -5736,7 +6038,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -5744,7 +6046,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -5752,7 +6054,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -5760,7 +6062,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -5768,7 +6070,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -5776,7 +6078,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -5784,7 +6086,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -5792,7 +6094,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -5800,7 +6102,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -5808,7 +6110,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -5816,7 +6118,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -5824,7 +6126,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -5832,7 +6134,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -5840,7 +6142,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -5848,7 +6150,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -5856,7 +6158,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -5864,7 +6166,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -5872,7 +6174,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -5880,7 +6182,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -5888,7 +6190,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -5896,7 +6198,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -5904,7 +6206,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -5912,7 +6214,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -5920,7 +6222,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -5928,7 +6230,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -5936,7 +6238,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -5944,7 +6246,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -5952,7 +6254,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -5960,7 +6262,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -5968,7 +6270,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -5976,7 +6278,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -5984,7 +6286,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -5992,7 +6294,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -6000,7 +6302,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -6008,7 +6310,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -6016,7 +6318,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -6024,7 +6326,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -6032,7 +6334,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -6040,7 +6342,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -6048,7 +6350,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -6056,7 +6358,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -6064,7 +6366,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -6072,7 +6374,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -6080,7 +6382,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -6088,7 +6390,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -6096,7 +6398,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -6113,7 +6415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -6140,13 +6442,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6160,7 +6462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -6168,7 +6470,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -6176,7 +6478,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -6184,7 +6486,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -6192,7 +6494,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -6200,7 +6502,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -6208,7 +6510,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -6216,7 +6518,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -6224,7 +6526,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -6232,7 +6534,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -6240,7 +6542,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -6248,7 +6550,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -6256,7 +6558,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -6264,7 +6566,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -6272,7 +6574,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -6280,7 +6582,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -6288,7 +6590,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -6296,7 +6598,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -6304,7 +6606,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -6312,7 +6614,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -6320,7 +6622,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -6328,7 +6630,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -6336,7 +6638,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -6344,7 +6646,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -6352,7 +6654,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -6360,7 +6662,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -6368,7 +6670,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -6376,7 +6678,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -6384,7 +6686,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -6392,7 +6694,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -6400,7 +6702,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -6408,7 +6710,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -6416,7 +6718,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -6424,7 +6726,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -6432,7 +6734,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -6440,7 +6742,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -6448,7 +6750,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -6456,7 +6758,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -6464,7 +6766,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -6472,7 +6774,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -6480,7 +6782,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -6488,7 +6790,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -6496,7 +6798,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -6504,7 +6806,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -6512,7 +6814,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -6520,7 +6822,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -6528,7 +6830,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -6536,7 +6838,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -6544,7 +6846,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -6552,7 +6854,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -6560,7 +6862,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -6568,7 +6870,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -6576,7 +6878,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -6584,7 +6886,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -6601,7 +6903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -6628,13 +6930,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6648,7 +6950,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -6656,7 +6958,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -6664,7 +6966,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -6672,7 +6974,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -6680,7 +6982,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -6688,7 +6990,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -6696,7 +6998,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -6704,7 +7006,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -6712,7 +7014,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -6720,7 +7022,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -6728,7 +7030,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -6736,7 +7038,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -6744,7 +7046,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -6752,7 +7054,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -6760,7 +7062,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -6768,7 +7070,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -6776,7 +7078,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -6784,7 +7086,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -6792,7 +7094,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -6800,7 +7102,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -6808,7 +7110,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -6816,7 +7118,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -6824,7 +7126,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -6832,7 +7134,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -6840,7 +7142,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -6848,7 +7150,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -6856,7 +7158,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -6864,7 +7166,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -6872,7 +7174,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -6880,7 +7182,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -6888,7 +7190,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -6896,7 +7198,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -6904,7 +7206,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -6912,7 +7214,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -6920,7 +7222,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -6928,7 +7230,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -6936,7 +7238,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -6944,7 +7246,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -6952,7 +7254,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -6960,7 +7262,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -6968,7 +7270,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -6976,7 +7278,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -6984,7 +7286,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -6992,7 +7294,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -7000,7 +7302,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -7008,7 +7310,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -7016,7 +7318,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -7024,7 +7326,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -7032,7 +7334,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -7040,7 +7342,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -7048,7 +7350,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -7056,7 +7358,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -7064,7 +7366,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -7072,7 +7374,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -7089,7 +7391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -7116,13 +7418,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7136,7 +7438,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -7144,7 +7446,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -7152,7 +7454,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -7160,7 +7462,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -7168,7 +7470,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -7176,7 +7478,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -7184,7 +7486,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -7192,7 +7494,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -7200,7 +7502,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -7208,7 +7510,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -7216,7 +7518,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -7224,7 +7526,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -7232,7 +7534,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -7240,7 +7542,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -7248,7 +7550,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -7256,7 +7558,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -7264,7 +7566,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -7272,7 +7574,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -7280,7 +7582,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -7288,7 +7590,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -7296,7 +7598,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -7304,7 +7606,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -7312,7 +7614,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -7320,7 +7622,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -7328,7 +7630,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -7336,7 +7638,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -7344,7 +7646,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -7352,7 +7654,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -7360,7 +7662,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -7368,7 +7670,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -7376,7 +7678,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -7384,7 +7686,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -7392,7 +7694,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -7400,7 +7702,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -7408,7 +7710,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -7416,7 +7718,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -7424,7 +7726,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -7432,7 +7734,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -7440,7 +7742,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -7448,7 +7750,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -7456,7 +7758,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -7464,7 +7766,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -7472,7 +7774,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -7480,7 +7782,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -7488,7 +7790,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -7496,7 +7798,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -7504,7 +7806,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -7512,7 +7814,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -7520,7 +7822,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -7528,7 +7830,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -7536,7 +7838,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -7544,7 +7846,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -7552,7 +7854,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -7560,7 +7862,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -7577,7 +7879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -7604,13 +7906,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7624,7 +7926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -7632,7 +7934,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -7640,7 +7942,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -7648,7 +7950,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -7656,7 +7958,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -7664,7 +7966,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -7672,7 +7974,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -7680,7 +7982,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -7688,7 +7990,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -7696,7 +7998,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -7704,7 +8006,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -7712,7 +8014,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -7720,7 +8022,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -7728,7 +8030,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -7736,7 +8038,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -7744,7 +8046,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -7752,7 +8054,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -7760,7 +8062,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -7768,7 +8070,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -7776,7 +8078,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -7784,7 +8086,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -7792,7 +8094,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -7800,7 +8102,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -7808,7 +8110,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -7816,7 +8118,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -7824,7 +8126,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -7832,7 +8134,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -7840,7 +8142,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -7848,7 +8150,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -7856,7 +8158,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -7864,7 +8166,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -7872,7 +8174,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -7880,7 +8182,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -7888,7 +8190,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -7896,7 +8198,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -7904,7 +8206,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -7912,7 +8214,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -7920,7 +8222,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -7928,7 +8230,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -7936,7 +8238,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -7944,7 +8246,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -7952,7 +8254,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -7960,7 +8262,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -7968,7 +8270,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -7976,7 +8278,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -7984,7 +8286,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -7992,7 +8294,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -8000,7 +8302,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -8008,7 +8310,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -8016,7 +8318,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -8024,7 +8326,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -8032,7 +8334,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -8040,7 +8342,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -8048,7 +8350,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -8065,7 +8367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -8092,13 +8394,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8112,7 +8414,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -8120,7 +8422,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -8128,7 +8430,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -8136,7 +8438,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -8144,7 +8446,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -8152,7 +8454,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -8160,7 +8462,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -8168,7 +8470,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -8176,7 +8478,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -8184,7 +8486,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -8192,7 +8494,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -8200,7 +8502,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -8208,7 +8510,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -8216,7 +8518,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -8224,7 +8526,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -8232,7 +8534,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -8240,7 +8542,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -8248,7 +8550,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -8256,7 +8558,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -8264,7 +8566,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -8272,7 +8574,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -8280,7 +8582,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -8288,7 +8590,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -8296,7 +8598,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -8304,7 +8606,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -8312,7 +8614,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -8320,7 +8622,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -8328,7 +8630,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -8336,7 +8638,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -8344,7 +8646,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -8352,7 +8654,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -8360,7 +8662,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -8368,7 +8670,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -8376,7 +8678,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -8384,7 +8686,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -8392,7 +8694,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -8400,7 +8702,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -8408,7 +8710,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -8416,7 +8718,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -8424,7 +8726,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -8432,7 +8734,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -8440,7 +8742,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -8448,7 +8750,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -8456,7 +8758,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -8464,7 +8766,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -8472,7 +8774,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -8480,7 +8782,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -8488,7 +8790,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -8496,7 +8798,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -8504,7 +8806,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -8512,7 +8814,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -8520,7 +8822,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -8528,7 +8830,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -8536,7 +8838,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -8553,7 +8855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>

--- a/statistics_files/2026/2026_99_gc_sharing.xlsx
+++ b/statistics_files/2026/2026_99_gc_sharing.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Staff\Documents\GitHub\next_statistics\statistics_files\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F118B7-5011-4BBC-BF7B-22F5DDE96F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BA14E6-CDEC-4965-962C-1CAD16C7C616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -1149,13 +1149,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="4" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="4" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>5663</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>3255</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>9155</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -1301,7 +1301,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>2530</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>11305</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -1505,7 +1505,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>2580</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>6895</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>3290</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>3565</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>3880</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -1941,13 +1941,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="4" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="4" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1969,7 +1969,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1977,7 +1977,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -1985,7 +1985,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1993,7 +1993,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -2001,7 +2001,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -2009,7 +2009,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -2017,7 +2017,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -2025,7 +2025,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -2033,7 +2033,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -2041,7 +2041,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -2049,7 +2049,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -2057,7 +2057,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -2065,7 +2065,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -2073,7 +2073,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -2081,7 +2081,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -2089,7 +2089,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -2097,7 +2097,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -2105,7 +2105,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -2113,7 +2113,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -2121,7 +2121,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -2129,7 +2129,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -2137,7 +2137,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -2145,7 +2145,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -2153,7 +2153,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -2161,7 +2161,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -2169,7 +2169,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -2177,7 +2177,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -2185,7 +2185,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -2193,7 +2193,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -2201,7 +2201,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -2209,7 +2209,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -2217,7 +2217,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -2225,7 +2225,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -2233,7 +2233,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -2241,7 +2241,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -2249,7 +2249,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -2257,7 +2257,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -2265,7 +2265,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -2273,7 +2273,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -2281,7 +2281,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -2289,7 +2289,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -2297,7 +2297,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -2305,7 +2305,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -2313,7 +2313,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -2321,7 +2321,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -2329,7 +2329,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -2337,7 +2337,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -2345,7 +2345,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -2353,7 +2353,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -2361,7 +2361,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -2369,7 +2369,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -2385,7 +2385,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -2429,13 +2429,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="4" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="4" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2457,7 +2457,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -2465,7 +2465,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -2473,7 +2473,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2481,7 +2481,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -2489,7 +2489,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -2497,7 +2497,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -2505,7 +2505,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -2513,7 +2513,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -2521,7 +2521,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -2529,7 +2529,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -2537,7 +2537,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -2545,7 +2545,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -2553,7 +2553,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -2561,7 +2561,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -2569,7 +2569,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -2577,7 +2577,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -2585,7 +2585,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -2593,7 +2593,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -2601,7 +2601,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -2609,7 +2609,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -2617,7 +2617,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -2625,7 +2625,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -2633,7 +2633,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -2641,7 +2641,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -2649,7 +2649,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -2657,7 +2657,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -2665,7 +2665,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -2673,7 +2673,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -2681,7 +2681,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -2689,7 +2689,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -2697,7 +2697,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -2705,7 +2705,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -2713,7 +2713,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -2721,7 +2721,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -2729,7 +2729,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -2737,7 +2737,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -2745,7 +2745,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -2753,7 +2753,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -2761,7 +2761,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -2769,7 +2769,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -2777,7 +2777,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -2785,7 +2785,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -2793,7 +2793,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -2801,7 +2801,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -2809,7 +2809,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -2817,7 +2817,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -2825,7 +2825,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -2833,7 +2833,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -2841,7 +2841,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -2849,7 +2849,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -2857,7 +2857,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -2865,7 +2865,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -2873,7 +2873,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -2917,13 +2917,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="4" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="4" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2945,7 +2945,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -2953,7 +2953,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -2961,7 +2961,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2969,7 +2969,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -2977,7 +2977,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -2985,7 +2985,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -2993,7 +2993,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -3001,7 +3001,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -3009,7 +3009,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -3017,7 +3017,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -3025,7 +3025,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -3033,7 +3033,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -3041,7 +3041,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -3049,7 +3049,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -3057,7 +3057,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -3065,7 +3065,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -3073,7 +3073,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -3081,7 +3081,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -3089,7 +3089,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -3097,7 +3097,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -3105,7 +3105,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -3113,7 +3113,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -3121,7 +3121,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -3129,7 +3129,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -3137,7 +3137,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -3145,7 +3145,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -3153,7 +3153,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -3161,7 +3161,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -3169,7 +3169,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -3177,7 +3177,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -3185,7 +3185,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -3193,7 +3193,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -3201,7 +3201,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -3209,7 +3209,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -3217,7 +3217,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -3225,7 +3225,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -3233,7 +3233,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -3241,7 +3241,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -3249,7 +3249,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -3257,7 +3257,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -3265,7 +3265,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -3273,7 +3273,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -3281,7 +3281,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -3289,7 +3289,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -3297,7 +3297,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -3305,7 +3305,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -3313,7 +3313,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -3321,7 +3321,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -3329,7 +3329,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -3337,7 +3337,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -3345,7 +3345,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -3353,7 +3353,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -3361,7 +3361,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -3405,13 +3405,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="4" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="4" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3425,149 +3425,149 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3">
         <f>SUM(January:December!B2)</f>
-        <v>12222</v>
+        <v>16023</v>
       </c>
       <c r="C2" s="3">
         <f>SUM(January:December!C2)</f>
-        <v>4403</v>
+        <v>5856</v>
       </c>
       <c r="D2" s="3">
         <f>SUM(January:December!D2)</f>
-        <v>16625</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>21879</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="4">
         <f>SUM(January:December!B3)</f>
-        <v>7731</v>
+        <v>10056</v>
       </c>
       <c r="C3" s="4">
         <f>SUM(January:December!C3)</f>
-        <v>1993</v>
+        <v>2499</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(January:December!D3)</f>
-        <v>9724</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>12555</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="3">
         <f>SUM(January:December!B4)</f>
-        <v>22884</v>
+        <v>29953</v>
       </c>
       <c r="C4" s="3">
         <f>SUM(January:December!C4)</f>
-        <v>3822</v>
+        <v>4858</v>
       </c>
       <c r="D4" s="3">
         <f>SUM(January:December!D4)</f>
-        <v>26706</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>34811</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>SUM(January:December!B5)</f>
-        <v>220</v>
+        <v>327</v>
       </c>
       <c r="C5" s="4">
         <f>SUM(January:December!C5)</f>
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="D5" s="4">
         <f>SUM(January:December!D5)</f>
-        <v>278</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="3">
         <f>SUM(January:December!B6)</f>
-        <v>15023</v>
+        <v>20083</v>
       </c>
       <c r="C6" s="3">
         <f>SUM(January:December!C6)</f>
-        <v>3189</v>
+        <v>4094</v>
       </c>
       <c r="D6" s="3">
         <f>SUM(January:December!D6)</f>
-        <v>18212</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>24177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>SUM(January:December!B7)</f>
-        <v>2054</v>
+        <v>2829</v>
       </c>
       <c r="C7" s="4">
         <f>SUM(January:December!C7)</f>
-        <v>614</v>
+        <v>850</v>
       </c>
       <c r="D7" s="4">
         <f>SUM(January:December!D7)</f>
-        <v>2668</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3679</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="3">
         <f>SUM(January:December!B8)</f>
-        <v>1276</v>
+        <v>1594</v>
       </c>
       <c r="C8" s="3">
         <f>SUM(January:December!C8)</f>
-        <v>362</v>
+        <v>446</v>
       </c>
       <c r="D8" s="3">
         <f>SUM(January:December!D8)</f>
-        <v>1638</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>SUM(January:December!B9)</f>
-        <v>517</v>
+        <v>705</v>
       </c>
       <c r="C9" s="4">
         <f>SUM(January:December!C9)</f>
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="D9" s="4">
         <f>SUM(January:December!D9)</f>
-        <v>702</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="3">
         <f>SUM(January:December!B10)</f>
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="C10" s="3">
         <f>SUM(January:December!C10)</f>
@@ -3575,10 +3575,10 @@
       </c>
       <c r="D10" s="3">
         <f>SUM(January:December!D10)</f>
-        <v>143</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -3595,245 +3595,245 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="5">
         <f>SUM(January:December!B12)</f>
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="C12" s="5">
         <f>SUM(January:December!C12)</f>
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D12" s="5">
         <f>SUM(January:December!D12)</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="6">
         <f>SUM(January:December!B13)</f>
-        <v>326</v>
+        <v>480</v>
       </c>
       <c r="C13" s="6">
         <f>SUM(January:December!C13)</f>
-        <v>163</v>
+        <v>218</v>
       </c>
       <c r="D13" s="6">
         <f>SUM(January:December!D13)</f>
-        <v>489</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>1845</v>
+        <v>2414</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>431</v>
+        <v>547</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>2276</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2961</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="6">
         <f>SUM(January:December!B15)</f>
-        <v>772</v>
+        <v>1014</v>
       </c>
       <c r="C15" s="6">
         <f>SUM(January:December!C15)</f>
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="D15" s="6">
         <f>SUM(January:December!D15)</f>
-        <v>924</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B16" s="3">
         <f>SUM(January:December!B16)</f>
-        <v>657</v>
+        <v>912</v>
       </c>
       <c r="C16" s="3">
         <f>SUM(January:December!C16)</f>
-        <v>187</v>
+        <v>259</v>
       </c>
       <c r="D16" s="3">
         <f>SUM(January:December!D16)</f>
-        <v>844</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>SUM(January:December!B17)</f>
-        <v>3612</v>
+        <v>4708</v>
       </c>
       <c r="C17" s="4">
         <f>SUM(January:December!C17)</f>
-        <v>2118</v>
+        <v>2686</v>
       </c>
       <c r="D17" s="4">
         <f>SUM(January:December!D17)</f>
-        <v>5730</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>7394</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
         <f>SUM(January:December!B18)</f>
-        <v>285</v>
+        <v>365</v>
       </c>
       <c r="C18" s="3">
         <f>SUM(January:December!C18)</f>
-        <v>276</v>
+        <v>399</v>
       </c>
       <c r="D18" s="3">
         <f>SUM(January:December!D18)</f>
-        <v>561</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>SUM(January:December!B19)</f>
-        <v>4622</v>
+        <v>6202</v>
       </c>
       <c r="C19" s="4">
         <f>SUM(January:December!C19)</f>
-        <v>1789</v>
+        <v>2207</v>
       </c>
       <c r="D19" s="4">
         <f>SUM(January:December!D19)</f>
-        <v>6411</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>8409</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="3">
         <f>SUM(January:December!B20)</f>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C20" s="3">
         <f>SUM(January:December!C20)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D20" s="3">
         <f>SUM(January:December!D20)</f>
-        <v>98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="4">
         <f>SUM(January:December!B21)</f>
-        <v>4457</v>
+        <v>5888</v>
       </c>
       <c r="C21" s="4">
         <f>SUM(January:December!C21)</f>
-        <v>1512</v>
+        <v>1958</v>
       </c>
       <c r="D21" s="4">
         <f>SUM(January:December!D21)</f>
-        <v>5969</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>7846</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="3">
         <f>SUM(January:December!B22)</f>
-        <v>690</v>
+        <v>974</v>
       </c>
       <c r="C22" s="3">
         <f>SUM(January:December!C22)</f>
-        <v>287</v>
+        <v>377</v>
       </c>
       <c r="D22" s="3">
         <f>SUM(January:December!D22)</f>
-        <v>977</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="4">
         <f>SUM(January:December!B23)</f>
-        <v>6222</v>
+        <v>8559</v>
       </c>
       <c r="C23" s="4">
         <f>SUM(January:December!C23)</f>
-        <v>2054</v>
+        <v>2688</v>
       </c>
       <c r="D23" s="4">
         <f>SUM(January:December!D23)</f>
-        <v>8276</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11247</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B24" s="3">
         <f>SUM(January:December!B24)</f>
-        <v>28888</v>
+        <v>38396</v>
       </c>
       <c r="C24" s="3">
         <f>SUM(January:December!C24)</f>
-        <v>5484</v>
+        <v>7303</v>
       </c>
       <c r="D24" s="3">
         <f>SUM(January:December!D24)</f>
-        <v>34372</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>45699</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="4">
         <f>SUM(January:December!B25)</f>
-        <v>1217</v>
+        <v>1606</v>
       </c>
       <c r="C25" s="4">
         <f>SUM(January:December!C25)</f>
-        <v>463</v>
+        <v>678</v>
       </c>
       <c r="D25" s="4">
         <f>SUM(January:December!D25)</f>
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -3850,514 +3850,514 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="4">
         <f>SUM(January:December!B27)</f>
-        <v>1211</v>
+        <v>1619</v>
       </c>
       <c r="C27" s="4">
         <f>SUM(January:December!C27)</f>
-        <v>572</v>
+        <v>763</v>
       </c>
       <c r="D27" s="4">
         <f>SUM(January:December!D27)</f>
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B28" s="3">
         <f>SUM(January:December!B28)</f>
-        <v>959</v>
+        <v>1218</v>
       </c>
       <c r="C28" s="3">
         <f>SUM(January:December!C28)</f>
-        <v>411</v>
+        <v>539</v>
       </c>
       <c r="D28" s="3">
         <f>SUM(January:December!D28)</f>
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B29" s="4">
         <f>SUM(January:December!B29)</f>
-        <v>4943</v>
+        <v>6937</v>
       </c>
       <c r="C29" s="4">
         <f>SUM(January:December!C29)</f>
-        <v>2561</v>
+        <v>3337</v>
       </c>
       <c r="D29" s="4">
         <f>SUM(January:December!D29)</f>
-        <v>7504</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10274</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B30" s="3">
         <f>SUM(January:December!B30)</f>
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C30" s="3">
         <f>SUM(January:December!C30)</f>
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="D30" s="3">
         <f>SUM(January:December!D30)</f>
-        <v>98</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B31" s="4">
         <f>SUM(January:December!B31)</f>
-        <v>1042</v>
+        <v>1334</v>
       </c>
       <c r="C31" s="4">
         <f>SUM(January:December!C31)</f>
-        <v>404</v>
+        <v>505</v>
       </c>
       <c r="D31" s="4">
         <f>SUM(January:December!D31)</f>
-        <v>1446</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B32" s="3">
         <f>SUM(January:December!B32)</f>
-        <v>3604</v>
+        <v>4741</v>
       </c>
       <c r="C32" s="3">
         <f>SUM(January:December!C32)</f>
-        <v>1349</v>
+        <v>1730</v>
       </c>
       <c r="D32" s="3">
         <f>SUM(January:December!D32)</f>
-        <v>4953</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B33" s="4">
         <f>SUM(January:December!B33)</f>
-        <v>2251</v>
+        <v>2987</v>
       </c>
       <c r="C33" s="4">
         <f>SUM(January:December!C33)</f>
-        <v>1143</v>
+        <v>1453</v>
       </c>
       <c r="D33" s="4">
         <f>SUM(January:December!D33)</f>
-        <v>3394</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4440</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B34" s="3">
         <f>SUM(January:December!B34)</f>
-        <v>1367</v>
+        <v>1768</v>
       </c>
       <c r="C34" s="3">
         <f>SUM(January:December!C34)</f>
-        <v>581</v>
+        <v>724</v>
       </c>
       <c r="D34" s="3">
         <f>SUM(January:December!D34)</f>
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B35" s="4">
         <f>SUM(January:December!B35)</f>
-        <v>16465</v>
+        <v>18987</v>
       </c>
       <c r="C35" s="4">
         <f>SUM(January:December!C35)</f>
-        <v>2915</v>
+        <v>3958</v>
       </c>
       <c r="D35" s="4">
         <f>SUM(January:December!D35)</f>
-        <v>19380</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>22945</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B36" s="3">
         <f>SUM(January:December!B36)</f>
-        <v>2255</v>
+        <v>2901</v>
       </c>
       <c r="C36" s="3">
         <f>SUM(January:December!C36)</f>
-        <v>515</v>
+        <v>690</v>
       </c>
       <c r="D36" s="3">
         <f>SUM(January:December!D36)</f>
-        <v>2770</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3591</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B37" s="4">
         <f>SUM(January:December!B37)</f>
-        <v>8727</v>
+        <v>11484</v>
       </c>
       <c r="C37" s="4">
         <f>SUM(January:December!C37)</f>
-        <v>1709</v>
+        <v>2337</v>
       </c>
       <c r="D37" s="4">
         <f>SUM(January:December!D37)</f>
-        <v>10436</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>13821</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B38" s="3">
         <f>SUM(January:December!B38)</f>
-        <v>528</v>
+        <v>777</v>
       </c>
       <c r="C38" s="3">
         <f>SUM(January:December!C38)</f>
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="D38" s="3">
         <f>SUM(January:December!D38)</f>
-        <v>614</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B39" s="4">
         <f>SUM(January:December!B39)</f>
-        <v>299</v>
+        <v>377</v>
       </c>
       <c r="C39" s="4">
         <f>SUM(January:December!C39)</f>
-        <v>558</v>
+        <v>628</v>
       </c>
       <c r="D39" s="4">
         <f>SUM(January:December!D39)</f>
-        <v>857</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B40" s="7">
         <f>SUM(January:December!B40)</f>
-        <v>1283</v>
+        <v>1832</v>
       </c>
       <c r="C40" s="7">
         <f>SUM(January:December!C40)</f>
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D40" s="7">
         <f>SUM(January:December!D40)</f>
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
       <c r="B41" s="8">
         <f>SUM(January:December!B41)</f>
-        <v>6596</v>
+        <v>8499</v>
       </c>
       <c r="C41" s="8">
         <f>SUM(January:December!C41)</f>
-        <v>347</v>
+        <v>444</v>
       </c>
       <c r="D41" s="8">
         <f>SUM(January:December!D41)</f>
-        <v>6943</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>8943</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B42" s="7">
         <f>SUM(January:December!B42)</f>
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(January:December!C42)</f>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D42" s="7">
         <f>SUM(January:December!D42)</f>
-        <v>145</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B43" s="8">
         <f>SUM(January:December!B43)</f>
-        <v>861</v>
+        <v>1086</v>
       </c>
       <c r="C43" s="8">
         <f>SUM(January:December!C43)</f>
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D43" s="8">
         <f>SUM(January:December!D43)</f>
-        <v>898</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B44" s="3">
         <f>SUM(January:December!B44)</f>
-        <v>945</v>
+        <v>1325</v>
       </c>
       <c r="C44" s="3">
         <f>SUM(January:December!C44)</f>
-        <v>176</v>
+        <v>243</v>
       </c>
       <c r="D44" s="3">
         <f>SUM(January:December!D44)</f>
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
       <c r="B45" s="4">
         <f>SUM(January:December!B45)</f>
-        <v>3746</v>
+        <v>5022</v>
       </c>
       <c r="C45" s="4">
         <f>SUM(January:December!C45)</f>
-        <v>1629</v>
+        <v>2179</v>
       </c>
       <c r="D45" s="4">
         <f>SUM(January:December!D45)</f>
-        <v>5375</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>7201</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B46" s="3">
         <f>SUM(January:December!B46)</f>
-        <v>7275</v>
+        <v>9462</v>
       </c>
       <c r="C46" s="3">
         <f>SUM(January:December!C46)</f>
-        <v>2910</v>
+        <v>3642</v>
       </c>
       <c r="D46" s="3">
         <f>SUM(January:December!D46)</f>
-        <v>10185</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>13104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B47" s="4">
         <f>SUM(January:December!B47)</f>
-        <v>3440</v>
+        <v>4823</v>
       </c>
       <c r="C47" s="4">
         <f>SUM(January:December!C47)</f>
-        <v>720</v>
+        <v>960</v>
       </c>
       <c r="D47" s="4">
         <f>SUM(January:December!D47)</f>
-        <v>4160</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5783</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B48" s="3">
         <f>SUM(January:December!B48)</f>
-        <v>1455</v>
+        <v>1963</v>
       </c>
       <c r="C48" s="3">
         <f>SUM(January:December!C48)</f>
-        <v>1456</v>
+        <v>1850</v>
       </c>
       <c r="D48" s="3">
         <f>SUM(January:December!D48)</f>
-        <v>2911</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3813</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B49" s="4">
         <f>SUM(January:December!B49)</f>
-        <v>9015</v>
+        <v>11776</v>
       </c>
       <c r="C49" s="4">
         <f>SUM(January:December!C49)</f>
-        <v>2751</v>
+        <v>3735</v>
       </c>
       <c r="D49" s="4">
         <f>SUM(January:December!D49)</f>
-        <v>11766</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>15511</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B50" s="3">
         <f>SUM(January:December!B50)</f>
-        <v>952</v>
+        <v>1363</v>
       </c>
       <c r="C50" s="3">
         <f>SUM(January:December!C50)</f>
-        <v>382</v>
+        <v>513</v>
       </c>
       <c r="D50" s="3">
         <f>SUM(January:December!D50)</f>
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B51" s="4">
         <f>SUM(January:December!B51)</f>
-        <v>2587</v>
+        <v>3496</v>
       </c>
       <c r="C51" s="4">
         <f>SUM(January:December!C51)</f>
-        <v>1672</v>
+        <v>2021</v>
       </c>
       <c r="D51" s="4">
         <f>SUM(January:December!D51)</f>
-        <v>4259</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5517</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B52" s="3">
         <f>SUM(January:December!B52)</f>
-        <v>236</v>
+        <v>318</v>
       </c>
       <c r="C52" s="3">
         <f>SUM(January:December!C52)</f>
-        <v>413</v>
+        <v>543</v>
       </c>
       <c r="D52" s="3">
         <f>SUM(January:December!D52)</f>
-        <v>649</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
       <c r="B53" s="4">
         <f>SUM(January:December!B53)</f>
-        <v>591</v>
+        <v>892</v>
       </c>
       <c r="C53" s="4">
         <f>SUM(January:December!C53)</f>
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="D53" s="4">
         <f>SUM(January:December!D53)</f>
-        <v>673</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B54" s="3">
         <f>SUM(January:December!B54)</f>
-        <v>826</v>
+        <v>1050</v>
       </c>
       <c r="C54" s="3">
         <f>SUM(January:December!C54)</f>
-        <v>1204</v>
+        <v>1683</v>
       </c>
       <c r="D54" s="3">
         <f>SUM(January:December!D54)</f>
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2733</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>2993</v>
+        <v>4004</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>758</v>
+        <v>977</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>3751</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4981</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B56" s="8">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>8867</v>
+        <v>11565</v>
       </c>
       <c r="C56" s="8">
         <f t="shared" ref="C56:D56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>466</v>
+        <v>593</v>
       </c>
       <c r="D56" s="8">
         <f t="shared" si="1"/>
-        <v>9333</v>
+        <v>12158</v>
       </c>
     </row>
   </sheetData>
@@ -4370,13 +4370,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="4" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="4" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>5122</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>3066</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>8064</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>5650</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -4524,7 +4524,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>10990</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -4728,7 +4728,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>2376</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>6409</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -4882,7 +4882,7 @@
         <v>3292</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -4896,7 +4896,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -4924,7 +4924,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>3081</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>3788</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -5106,7 +5106,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -5164,13 +5164,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="4" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="4" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>5840</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>3403</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>9487</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -5282,7 +5282,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -5316,7 +5316,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -5358,7 +5358,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -5386,7 +5386,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>3233</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -5496,7 +5496,7 @@
         <v>12077</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -5518,7 +5518,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -5546,7 +5546,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -5574,7 +5574,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -5588,7 +5588,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>6076</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>3854</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -5686,7 +5686,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -5700,7 +5700,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -5728,7 +5728,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -5770,7 +5770,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -5798,7 +5798,7 @@
         <v>3539</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -5812,7 +5812,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>4098</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -5854,7 +5854,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -5868,7 +5868,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -5896,7 +5896,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -5954,13 +5954,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="4" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="4" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5974,79 +5974,131 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="3">
+        <v>3801</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1453</v>
+      </c>
+      <c r="D2" s="3">
+        <v>5254</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="4">
+        <v>2325</v>
+      </c>
+      <c r="C3" s="4">
+        <v>506</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="3">
+        <v>7069</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1036</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="4">
+        <v>107</v>
+      </c>
+      <c r="C5" s="4">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="3">
+        <v>5060</v>
+      </c>
+      <c r="C6" s="3">
+        <v>905</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5965</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="4">
+        <v>775</v>
+      </c>
+      <c r="C7" s="4">
+        <v>236</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="3">
+        <v>318</v>
+      </c>
+      <c r="C8" s="3">
+        <v>84</v>
+      </c>
+      <c r="D8" s="3">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="4">
+        <v>188</v>
+      </c>
+      <c r="C9" s="4">
+        <v>44</v>
+      </c>
+      <c r="D9" s="4">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="3">
+        <v>59</v>
+      </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -6054,119 +6106,203 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="5">
+        <v>46</v>
+      </c>
+      <c r="C12" s="5">
+        <v>11</v>
+      </c>
+      <c r="D12" s="5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="6">
+        <v>154</v>
+      </c>
+      <c r="C13" s="6">
+        <v>55</v>
+      </c>
+      <c r="D13" s="6">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="5">
+        <v>569</v>
+      </c>
+      <c r="C14" s="5">
+        <v>116</v>
+      </c>
+      <c r="D14" s="5">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="6">
+        <v>242</v>
+      </c>
+      <c r="C15" s="6">
+        <v>37</v>
+      </c>
+      <c r="D15" s="6">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="3">
+        <v>255</v>
+      </c>
+      <c r="C16" s="3">
+        <v>72</v>
+      </c>
+      <c r="D16" s="3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="4">
+        <v>1096</v>
+      </c>
+      <c r="C17" s="4">
+        <v>568</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="3">
+        <v>80</v>
+      </c>
+      <c r="C18" s="3">
+        <v>123</v>
+      </c>
+      <c r="D18" s="3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="4">
+        <v>1580</v>
+      </c>
+      <c r="C19" s="4">
+        <v>418</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="3">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2</v>
+      </c>
+      <c r="D20" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="4">
+        <v>1431</v>
+      </c>
+      <c r="C21" s="4">
+        <v>446</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="3">
+        <v>284</v>
+      </c>
+      <c r="C22" s="3">
+        <v>90</v>
+      </c>
+      <c r="D22" s="3">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="4">
+        <v>2337</v>
+      </c>
+      <c r="C23" s="4">
+        <v>634</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="3">
+        <v>9508</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1819</v>
+      </c>
+      <c r="D24" s="3">
+        <v>11327</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="4">
+        <v>389</v>
+      </c>
+      <c r="C25" s="4">
+        <v>215</v>
+      </c>
+      <c r="D25" s="4">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -6174,262 +6310,430 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="4">
+        <v>408</v>
+      </c>
+      <c r="C27" s="4">
+        <v>191</v>
+      </c>
+      <c r="D27" s="4">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="3">
+        <v>259</v>
+      </c>
+      <c r="C28" s="3">
+        <v>128</v>
+      </c>
+      <c r="D28" s="3">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="4">
+        <v>1994</v>
+      </c>
+      <c r="C29" s="4">
+        <v>776</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2770</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="3">
+        <v>15</v>
+      </c>
+      <c r="C30" s="3">
+        <v>70</v>
+      </c>
+      <c r="D30" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="4">
+        <v>292</v>
+      </c>
+      <c r="C31" s="4">
+        <v>101</v>
+      </c>
+      <c r="D31" s="4">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="3">
+        <v>1137</v>
+      </c>
+      <c r="C32" s="3">
+        <v>381</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="4">
+        <v>736</v>
+      </c>
+      <c r="C33" s="4">
+        <v>310</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-    </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="3">
+        <v>401</v>
+      </c>
+      <c r="C34" s="3">
+        <v>143</v>
+      </c>
+      <c r="D34" s="3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="4">
+        <v>2522</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1043</v>
+      </c>
+      <c r="D35" s="4">
+        <v>3565</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-    </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="3">
+        <v>646</v>
+      </c>
+      <c r="C36" s="3">
+        <v>175</v>
+      </c>
+      <c r="D36" s="3">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-    </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="4">
+        <v>2757</v>
+      </c>
+      <c r="C37" s="4">
+        <v>628</v>
+      </c>
+      <c r="D37" s="4">
+        <v>3385</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-    </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="3">
+        <v>249</v>
+      </c>
+      <c r="C38" s="3">
+        <v>48</v>
+      </c>
+      <c r="D38" s="3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-    </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="4">
+        <v>78</v>
+      </c>
+      <c r="C39" s="4">
+        <v>70</v>
+      </c>
+      <c r="D39" s="4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-    </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="7">
+        <v>549</v>
+      </c>
+      <c r="C40" s="7">
+        <v>11</v>
+      </c>
+      <c r="D40" s="7">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="8">
+        <v>1903</v>
+      </c>
+      <c r="C41" s="8">
+        <v>97</v>
+      </c>
+      <c r="D41" s="8">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-    </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="7">
+        <v>21</v>
+      </c>
+      <c r="C42" s="7">
+        <v>5</v>
+      </c>
+      <c r="D42" s="7">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="8">
+        <v>225</v>
+      </c>
+      <c r="C43" s="8">
+        <v>14</v>
+      </c>
+      <c r="D43" s="8">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-    </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="3">
+        <v>380</v>
+      </c>
+      <c r="C44" s="3">
+        <v>67</v>
+      </c>
+      <c r="D44" s="3">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="4">
+        <v>1276</v>
+      </c>
+      <c r="C45" s="4">
+        <v>550</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="3">
+        <v>2187</v>
+      </c>
+      <c r="C46" s="3">
+        <v>732</v>
+      </c>
+      <c r="D46" s="3">
+        <v>2919</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="4">
+        <v>1383</v>
+      </c>
+      <c r="C47" s="4">
+        <v>240</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-    </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="3">
+        <v>508</v>
+      </c>
+      <c r="C48" s="3">
+        <v>394</v>
+      </c>
+      <c r="D48" s="3">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-    </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="4">
+        <v>2761</v>
+      </c>
+      <c r="C49" s="4">
+        <v>984</v>
+      </c>
+      <c r="D49" s="4">
+        <v>3745</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-    </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="3">
+        <v>411</v>
+      </c>
+      <c r="C50" s="3">
+        <v>131</v>
+      </c>
+      <c r="D50" s="3">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-    </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="4">
+        <v>909</v>
+      </c>
+      <c r="C51" s="4">
+        <v>349</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-    </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="3">
+        <v>82</v>
+      </c>
+      <c r="C52" s="3">
+        <v>130</v>
+      </c>
+      <c r="D52" s="3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-    </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="4">
+        <v>301</v>
+      </c>
+      <c r="C53" s="4">
+        <v>29</v>
+      </c>
+      <c r="D53" s="4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-    </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="3">
+        <v>224</v>
+      </c>
+      <c r="C54" s="3">
+        <v>479</v>
+      </c>
+      <c r="D54" s="3">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B56" s="8">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>0</v>
+        <v>2698</v>
       </c>
       <c r="C56" s="8">
         <f t="shared" ref="C56:D56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="D56" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2825</v>
       </c>
     </row>
   </sheetData>
@@ -6442,13 +6746,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="4" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="4" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6462,7 +6766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -6470,7 +6774,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -6478,7 +6782,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -6486,7 +6790,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -6494,7 +6798,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -6502,7 +6806,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -6510,7 +6814,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -6518,7 +6822,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -6526,7 +6830,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -6534,7 +6838,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -6542,7 +6846,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -6550,7 +6854,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -6558,7 +6862,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -6566,7 +6870,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -6574,7 +6878,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -6582,7 +6886,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -6590,7 +6894,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -6598,7 +6902,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -6606,7 +6910,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -6614,7 +6918,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -6622,7 +6926,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -6630,7 +6934,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -6638,7 +6942,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -6646,7 +6950,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -6654,7 +6958,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -6662,7 +6966,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -6670,7 +6974,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -6678,7 +6982,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -6686,7 +6990,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -6694,7 +6998,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -6702,7 +7006,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -6710,7 +7014,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -6718,7 +7022,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -6726,7 +7030,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -6734,7 +7038,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -6742,7 +7046,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -6750,7 +7054,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -6758,7 +7062,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -6766,7 +7070,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -6774,7 +7078,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -6782,7 +7086,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -6790,7 +7094,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -6798,7 +7102,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -6806,7 +7110,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -6814,7 +7118,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -6822,7 +7126,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -6830,7 +7134,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -6838,7 +7142,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -6846,7 +7150,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -6854,7 +7158,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -6862,7 +7166,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -6870,7 +7174,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -6878,7 +7182,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -6886,7 +7190,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -6903,7 +7207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -6930,13 +7234,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="4" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="4" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6950,7 +7254,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -6958,7 +7262,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -6966,7 +7270,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -6974,7 +7278,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -6982,7 +7286,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -6990,7 +7294,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -6998,7 +7302,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -7006,7 +7310,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -7014,7 +7318,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -7022,7 +7326,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -7030,7 +7334,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -7038,7 +7342,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -7046,7 +7350,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -7054,7 +7358,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -7062,7 +7366,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -7070,7 +7374,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -7078,7 +7382,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -7086,7 +7390,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -7094,7 +7398,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -7102,7 +7406,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -7110,7 +7414,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -7118,7 +7422,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -7126,7 +7430,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -7134,7 +7438,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -7142,7 +7446,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -7150,7 +7454,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -7158,7 +7462,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -7166,7 +7470,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -7174,7 +7478,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -7182,7 +7486,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -7190,7 +7494,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -7198,7 +7502,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -7206,7 +7510,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -7214,7 +7518,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -7222,7 +7526,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -7230,7 +7534,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -7238,7 +7542,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -7246,7 +7550,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -7254,7 +7558,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -7262,7 +7566,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -7270,7 +7574,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -7278,7 +7582,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -7286,7 +7590,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -7294,7 +7598,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -7302,7 +7606,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -7310,7 +7614,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -7318,7 +7622,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -7326,7 +7630,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -7334,7 +7638,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -7342,7 +7646,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -7350,7 +7654,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -7358,7 +7662,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -7366,7 +7670,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -7374,7 +7678,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -7391,7 +7695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -7418,13 +7722,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="4" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="4" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7438,7 +7742,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -7446,7 +7750,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -7454,7 +7758,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -7462,7 +7766,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -7470,7 +7774,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -7478,7 +7782,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -7486,7 +7790,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -7494,7 +7798,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -7502,7 +7806,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -7510,7 +7814,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -7518,7 +7822,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -7526,7 +7830,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -7534,7 +7838,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -7542,7 +7846,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -7550,7 +7854,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -7558,7 +7862,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -7566,7 +7870,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -7574,7 +7878,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -7582,7 +7886,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -7590,7 +7894,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -7598,7 +7902,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -7606,7 +7910,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -7614,7 +7918,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -7622,7 +7926,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -7630,7 +7934,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -7638,7 +7942,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -7646,7 +7950,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -7654,7 +7958,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -7662,7 +7966,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -7670,7 +7974,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -7678,7 +7982,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -7686,7 +7990,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -7694,7 +7998,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -7702,7 +8006,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -7710,7 +8014,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -7718,7 +8022,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -7726,7 +8030,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -7734,7 +8038,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -7742,7 +8046,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -7750,7 +8054,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -7758,7 +8062,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -7766,7 +8070,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -7774,7 +8078,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -7782,7 +8086,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -7790,7 +8094,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -7798,7 +8102,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -7806,7 +8110,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -7814,7 +8118,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -7822,7 +8126,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -7830,7 +8134,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -7838,7 +8142,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -7846,7 +8150,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -7854,7 +8158,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -7862,7 +8166,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -7879,7 +8183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -7906,13 +8210,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="4" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="4" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7926,7 +8230,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -7934,7 +8238,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -7942,7 +8246,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -7950,7 +8254,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -7958,7 +8262,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -7966,7 +8270,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -7974,7 +8278,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -7982,7 +8286,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -7990,7 +8294,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -7998,7 +8302,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -8006,7 +8310,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -8014,7 +8318,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -8022,7 +8326,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -8030,7 +8334,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -8038,7 +8342,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -8046,7 +8350,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -8054,7 +8358,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -8062,7 +8366,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -8070,7 +8374,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -8078,7 +8382,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -8086,7 +8390,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -8094,7 +8398,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -8102,7 +8406,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -8110,7 +8414,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -8118,7 +8422,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -8126,7 +8430,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -8134,7 +8438,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -8142,7 +8446,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -8150,7 +8454,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -8158,7 +8462,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -8166,7 +8470,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -8174,7 +8478,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -8182,7 +8486,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -8190,7 +8494,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -8198,7 +8502,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -8206,7 +8510,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -8214,7 +8518,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -8222,7 +8526,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -8230,7 +8534,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -8238,7 +8542,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -8246,7 +8550,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -8254,7 +8558,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -8262,7 +8566,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -8270,7 +8574,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -8278,7 +8582,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -8286,7 +8590,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -8294,7 +8598,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -8302,7 +8606,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -8310,7 +8614,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -8318,7 +8622,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -8326,7 +8630,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -8334,7 +8638,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -8342,7 +8646,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -8350,7 +8654,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -8367,7 +8671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>
@@ -8394,13 +8698,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="4" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="4" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8414,7 +8718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -8422,7 +8726,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -8430,7 +8734,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -8438,7 +8742,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -8446,7 +8750,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -8454,7 +8758,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -8462,7 +8766,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -8470,7 +8774,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -8478,7 +8782,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -8486,7 +8790,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -8494,7 +8798,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -8502,7 +8806,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -8510,7 +8814,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -8518,7 +8822,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -8526,7 +8830,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -8534,7 +8838,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -8542,7 +8846,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -8550,7 +8854,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -8558,7 +8862,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -8566,7 +8870,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -8574,7 +8878,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -8582,7 +8886,7 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -8590,7 +8894,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -8598,7 +8902,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -8606,7 +8910,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -8614,7 +8918,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -8622,7 +8926,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
@@ -8630,7 +8934,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -8638,7 +8942,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
@@ -8646,7 +8950,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -8654,7 +8958,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
@@ -8662,7 +8966,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -8670,7 +8974,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
@@ -8678,7 +8982,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -8686,7 +8990,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
@@ -8694,7 +8998,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -8702,7 +9006,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -8710,7 +9014,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -8718,7 +9022,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -8726,7 +9030,7 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
@@ -8734,7 +9038,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
@@ -8742,7 +9046,7 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
@@ -8750,7 +9054,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
@@ -8758,7 +9062,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -8766,7 +9070,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -8774,7 +9078,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -8782,7 +9086,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
@@ -8790,7 +9094,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -8798,7 +9102,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -8806,7 +9110,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -8814,7 +9118,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -8822,7 +9126,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -8830,7 +9134,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -8838,7 +9142,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -8855,7 +9159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>57</v>
       </c>

--- a/statistics_files/2026/2026_99_gc_sharing.xlsx
+++ b/statistics_files/2026/2026_99_gc_sharing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BA14E6-CDEC-4965-962C-1CAD16C7C616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04F947F-A2C7-467F-80BB-93D427264548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -3431,15 +3431,15 @@
       </c>
       <c r="B2" s="3">
         <f>SUM(January:December!B2)</f>
-        <v>16023</v>
+        <v>20717</v>
       </c>
       <c r="C2" s="3">
         <f>SUM(January:December!C2)</f>
-        <v>5856</v>
+        <v>7107</v>
       </c>
       <c r="D2" s="3">
         <f>SUM(January:December!D2)</f>
-        <v>21879</v>
+        <v>27824</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3448,15 +3448,15 @@
       </c>
       <c r="B3" s="4">
         <f>SUM(January:December!B3)</f>
-        <v>10056</v>
+        <v>13170</v>
       </c>
       <c r="C3" s="4">
         <f>SUM(January:December!C3)</f>
-        <v>2499</v>
+        <v>3000</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(January:December!D3)</f>
-        <v>12555</v>
+        <v>16170</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3465,15 +3465,15 @@
       </c>
       <c r="B4" s="3">
         <f>SUM(January:December!B4)</f>
-        <v>29953</v>
+        <v>37215</v>
       </c>
       <c r="C4" s="3">
         <f>SUM(January:December!C4)</f>
-        <v>4858</v>
+        <v>5813</v>
       </c>
       <c r="D4" s="3">
         <f>SUM(January:December!D4)</f>
-        <v>34811</v>
+        <v>43028</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3482,15 +3482,15 @@
       </c>
       <c r="B5" s="4">
         <f>SUM(January:December!B5)</f>
-        <v>327</v>
+        <v>478</v>
       </c>
       <c r="C5" s="4">
         <f>SUM(January:December!C5)</f>
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="D5" s="4">
         <f>SUM(January:December!D5)</f>
-        <v>405</v>
+        <v>575</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3499,15 +3499,15 @@
       </c>
       <c r="B6" s="3">
         <f>SUM(January:December!B6)</f>
-        <v>20083</v>
+        <v>25451</v>
       </c>
       <c r="C6" s="3">
         <f>SUM(January:December!C6)</f>
-        <v>4094</v>
+        <v>4985</v>
       </c>
       <c r="D6" s="3">
         <f>SUM(January:December!D6)</f>
-        <v>24177</v>
+        <v>30436</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3516,15 +3516,15 @@
       </c>
       <c r="B7" s="4">
         <f>SUM(January:December!B7)</f>
-        <v>2829</v>
+        <v>3363</v>
       </c>
       <c r="C7" s="4">
         <f>SUM(January:December!C7)</f>
-        <v>850</v>
+        <v>1259</v>
       </c>
       <c r="D7" s="4">
         <f>SUM(January:December!D7)</f>
-        <v>3679</v>
+        <v>4622</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3533,15 +3533,15 @@
       </c>
       <c r="B8" s="3">
         <f>SUM(January:December!B8)</f>
-        <v>1594</v>
+        <v>2041</v>
       </c>
       <c r="C8" s="3">
         <f>SUM(January:December!C8)</f>
-        <v>446</v>
+        <v>533</v>
       </c>
       <c r="D8" s="3">
         <f>SUM(January:December!D8)</f>
-        <v>2040</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3550,15 +3550,15 @@
       </c>
       <c r="B9" s="4">
         <f>SUM(January:December!B9)</f>
-        <v>705</v>
+        <v>949</v>
       </c>
       <c r="C9" s="4">
         <f>SUM(January:December!C9)</f>
-        <v>229</v>
+        <v>276</v>
       </c>
       <c r="D9" s="4">
         <f>SUM(January:December!D9)</f>
-        <v>934</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="B10" s="3">
         <f>SUM(January:December!B10)</f>
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="C10" s="3">
         <f>SUM(January:December!C10)</f>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="D10" s="3">
         <f>SUM(January:December!D10)</f>
-        <v>202</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3601,15 +3601,15 @@
       </c>
       <c r="B12" s="5">
         <f>SUM(January:December!B12)</f>
-        <v>96</v>
+        <v>155</v>
       </c>
       <c r="C12" s="5">
         <f>SUM(January:December!C12)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D12" s="5">
         <f>SUM(January:December!D12)</f>
-        <v>119</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3618,15 +3618,15 @@
       </c>
       <c r="B13" s="6">
         <f>SUM(January:December!B13)</f>
-        <v>480</v>
+        <v>620</v>
       </c>
       <c r="C13" s="6">
         <f>SUM(January:December!C13)</f>
-        <v>218</v>
+        <v>262</v>
       </c>
       <c r="D13" s="6">
         <f>SUM(January:December!D13)</f>
-        <v>698</v>
+        <v>882</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3635,15 +3635,15 @@
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>2414</v>
+        <v>3011</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>547</v>
+        <v>644</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>2961</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3652,15 +3652,15 @@
       </c>
       <c r="B15" s="6">
         <f>SUM(January:December!B15)</f>
-        <v>1014</v>
+        <v>1269</v>
       </c>
       <c r="C15" s="6">
         <f>SUM(January:December!C15)</f>
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="D15" s="6">
         <f>SUM(January:December!D15)</f>
-        <v>1203</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3669,15 +3669,15 @@
       </c>
       <c r="B16" s="3">
         <f>SUM(January:December!B16)</f>
-        <v>912</v>
+        <v>1121</v>
       </c>
       <c r="C16" s="3">
         <f>SUM(January:December!C16)</f>
-        <v>259</v>
+        <v>311</v>
       </c>
       <c r="D16" s="3">
         <f>SUM(January:December!D16)</f>
-        <v>1171</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3686,15 +3686,15 @@
       </c>
       <c r="B17" s="4">
         <f>SUM(January:December!B17)</f>
-        <v>4708</v>
+        <v>6105</v>
       </c>
       <c r="C17" s="4">
         <f>SUM(January:December!C17)</f>
-        <v>2686</v>
+        <v>3243</v>
       </c>
       <c r="D17" s="4">
         <f>SUM(January:December!D17)</f>
-        <v>7394</v>
+        <v>9348</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3703,15 +3703,15 @@
       </c>
       <c r="B18" s="3">
         <f>SUM(January:December!B18)</f>
-        <v>365</v>
+        <v>463</v>
       </c>
       <c r="C18" s="3">
         <f>SUM(January:December!C18)</f>
-        <v>399</v>
+        <v>466</v>
       </c>
       <c r="D18" s="3">
         <f>SUM(January:December!D18)</f>
-        <v>764</v>
+        <v>929</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3720,15 +3720,15 @@
       </c>
       <c r="B19" s="4">
         <f>SUM(January:December!B19)</f>
-        <v>6202</v>
+        <v>7856</v>
       </c>
       <c r="C19" s="4">
         <f>SUM(January:December!C19)</f>
-        <v>2207</v>
+        <v>2587</v>
       </c>
       <c r="D19" s="4">
         <f>SUM(January:December!D19)</f>
-        <v>8409</v>
+        <v>10443</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3737,15 +3737,15 @@
       </c>
       <c r="B20" s="3">
         <f>SUM(January:December!B20)</f>
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C20" s="3">
         <f>SUM(January:December!C20)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="3">
         <f>SUM(January:December!D20)</f>
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3754,15 +3754,15 @@
       </c>
       <c r="B21" s="4">
         <f>SUM(January:December!B21)</f>
-        <v>5888</v>
+        <v>7506</v>
       </c>
       <c r="C21" s="4">
         <f>SUM(January:December!C21)</f>
-        <v>1958</v>
+        <v>2468</v>
       </c>
       <c r="D21" s="4">
         <f>SUM(January:December!D21)</f>
-        <v>7846</v>
+        <v>9974</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3771,15 +3771,15 @@
       </c>
       <c r="B22" s="3">
         <f>SUM(January:December!B22)</f>
-        <v>974</v>
+        <v>1258</v>
       </c>
       <c r="C22" s="3">
         <f>SUM(January:December!C22)</f>
-        <v>377</v>
+        <v>445</v>
       </c>
       <c r="D22" s="3">
         <f>SUM(January:December!D22)</f>
-        <v>1351</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3788,15 +3788,15 @@
       </c>
       <c r="B23" s="4">
         <f>SUM(January:December!B23)</f>
-        <v>8559</v>
+        <v>9926</v>
       </c>
       <c r="C23" s="4">
         <f>SUM(January:December!C23)</f>
-        <v>2688</v>
+        <v>3167</v>
       </c>
       <c r="D23" s="4">
         <f>SUM(January:December!D23)</f>
-        <v>11247</v>
+        <v>13093</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3805,15 +3805,15 @@
       </c>
       <c r="B24" s="3">
         <f>SUM(January:December!B24)</f>
-        <v>38396</v>
+        <v>49797</v>
       </c>
       <c r="C24" s="3">
         <f>SUM(January:December!C24)</f>
-        <v>7303</v>
+        <v>9023</v>
       </c>
       <c r="D24" s="3">
         <f>SUM(January:December!D24)</f>
-        <v>45699</v>
+        <v>58820</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3822,15 +3822,15 @@
       </c>
       <c r="B25" s="4">
         <f>SUM(January:December!B25)</f>
-        <v>1606</v>
+        <v>2105</v>
       </c>
       <c r="C25" s="4">
         <f>SUM(January:December!C25)</f>
-        <v>678</v>
+        <v>801</v>
       </c>
       <c r="D25" s="4">
         <f>SUM(January:December!D25)</f>
-        <v>2284</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3856,15 +3856,15 @@
       </c>
       <c r="B27" s="4">
         <f>SUM(January:December!B27)</f>
-        <v>1619</v>
+        <v>2070</v>
       </c>
       <c r="C27" s="4">
         <f>SUM(January:December!C27)</f>
-        <v>763</v>
+        <v>988</v>
       </c>
       <c r="D27" s="4">
         <f>SUM(January:December!D27)</f>
-        <v>2382</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3873,15 +3873,15 @@
       </c>
       <c r="B28" s="3">
         <f>SUM(January:December!B28)</f>
-        <v>1218</v>
+        <v>1519</v>
       </c>
       <c r="C28" s="3">
         <f>SUM(January:December!C28)</f>
-        <v>539</v>
+        <v>709</v>
       </c>
       <c r="D28" s="3">
         <f>SUM(January:December!D28)</f>
-        <v>1757</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3890,15 +3890,15 @@
       </c>
       <c r="B29" s="4">
         <f>SUM(January:December!B29)</f>
-        <v>6937</v>
+        <v>9320</v>
       </c>
       <c r="C29" s="4">
         <f>SUM(January:December!C29)</f>
-        <v>3337</v>
+        <v>4127</v>
       </c>
       <c r="D29" s="4">
         <f>SUM(January:December!D29)</f>
-        <v>10274</v>
+        <v>13447</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3907,15 +3907,15 @@
       </c>
       <c r="B30" s="3">
         <f>SUM(January:December!B30)</f>
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C30" s="3">
         <f>SUM(January:December!C30)</f>
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="D30" s="3">
         <f>SUM(January:December!D30)</f>
-        <v>183</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3924,15 +3924,15 @@
       </c>
       <c r="B31" s="4">
         <f>SUM(January:December!B31)</f>
-        <v>1334</v>
+        <v>1660</v>
       </c>
       <c r="C31" s="4">
         <f>SUM(January:December!C31)</f>
-        <v>505</v>
+        <v>597</v>
       </c>
       <c r="D31" s="4">
         <f>SUM(January:December!D31)</f>
-        <v>1839</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3941,15 +3941,15 @@
       </c>
       <c r="B32" s="3">
         <f>SUM(January:December!B32)</f>
-        <v>4741</v>
+        <v>6125</v>
       </c>
       <c r="C32" s="3">
         <f>SUM(January:December!C32)</f>
-        <v>1730</v>
+        <v>2041</v>
       </c>
       <c r="D32" s="3">
         <f>SUM(January:December!D32)</f>
-        <v>6471</v>
+        <v>8166</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3958,15 +3958,15 @@
       </c>
       <c r="B33" s="4">
         <f>SUM(January:December!B33)</f>
-        <v>2987</v>
+        <v>3893</v>
       </c>
       <c r="C33" s="4">
         <f>SUM(January:December!C33)</f>
-        <v>1453</v>
+        <v>1748</v>
       </c>
       <c r="D33" s="4">
         <f>SUM(January:December!D33)</f>
-        <v>4440</v>
+        <v>5641</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3975,15 +3975,15 @@
       </c>
       <c r="B34" s="3">
         <f>SUM(January:December!B34)</f>
-        <v>1768</v>
+        <v>2278</v>
       </c>
       <c r="C34" s="3">
         <f>SUM(January:December!C34)</f>
-        <v>724</v>
+        <v>867</v>
       </c>
       <c r="D34" s="3">
         <f>SUM(January:December!D34)</f>
-        <v>2492</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3992,15 +3992,15 @@
       </c>
       <c r="B35" s="4">
         <f>SUM(January:December!B35)</f>
-        <v>18987</v>
+        <v>23545</v>
       </c>
       <c r="C35" s="4">
         <f>SUM(January:December!C35)</f>
-        <v>3958</v>
+        <v>4883</v>
       </c>
       <c r="D35" s="4">
         <f>SUM(January:December!D35)</f>
-        <v>22945</v>
+        <v>28428</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4009,15 +4009,15 @@
       </c>
       <c r="B36" s="3">
         <f>SUM(January:December!B36)</f>
-        <v>2901</v>
+        <v>3702</v>
       </c>
       <c r="C36" s="3">
         <f>SUM(January:December!C36)</f>
-        <v>690</v>
+        <v>850</v>
       </c>
       <c r="D36" s="3">
         <f>SUM(January:December!D36)</f>
-        <v>3591</v>
+        <v>4552</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4026,15 +4026,15 @@
       </c>
       <c r="B37" s="4">
         <f>SUM(January:December!B37)</f>
-        <v>11484</v>
+        <v>15043</v>
       </c>
       <c r="C37" s="4">
         <f>SUM(January:December!C37)</f>
-        <v>2337</v>
+        <v>2858</v>
       </c>
       <c r="D37" s="4">
         <f>SUM(January:December!D37)</f>
-        <v>13821</v>
+        <v>17901</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4043,15 +4043,15 @@
       </c>
       <c r="B38" s="3">
         <f>SUM(January:December!B38)</f>
-        <v>777</v>
+        <v>1104</v>
       </c>
       <c r="C38" s="3">
         <f>SUM(January:December!C38)</f>
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="D38" s="3">
         <f>SUM(January:December!D38)</f>
-        <v>911</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4060,15 +4060,15 @@
       </c>
       <c r="B39" s="4">
         <f>SUM(January:December!B39)</f>
-        <v>377</v>
+        <v>454</v>
       </c>
       <c r="C39" s="4">
         <f>SUM(January:December!C39)</f>
-        <v>628</v>
+        <v>767</v>
       </c>
       <c r="D39" s="4">
         <f>SUM(January:December!D39)</f>
-        <v>1005</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="B40" s="7">
         <f>SUM(January:December!B40)</f>
-        <v>1832</v>
+        <v>1934</v>
       </c>
       <c r="C40" s="7">
         <f>SUM(January:December!C40)</f>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="D40" s="7">
         <f>SUM(January:December!D40)</f>
-        <v>1907</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4094,15 +4094,15 @@
       </c>
       <c r="B41" s="8">
         <f>SUM(January:December!B41)</f>
-        <v>8499</v>
+        <v>8521</v>
       </c>
       <c r="C41" s="8">
         <f>SUM(January:December!C41)</f>
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D41" s="8">
         <f>SUM(January:December!D41)</f>
-        <v>8943</v>
+        <v>8969</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="B42" s="7">
         <f>SUM(January:December!B42)</f>
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(January:December!C42)</f>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="D42" s="7">
         <f>SUM(January:December!D42)</f>
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4145,15 +4145,15 @@
       </c>
       <c r="B44" s="3">
         <f>SUM(January:December!B44)</f>
-        <v>1325</v>
+        <v>1688</v>
       </c>
       <c r="C44" s="3">
         <f>SUM(January:December!C44)</f>
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="D44" s="3">
         <f>SUM(January:December!D44)</f>
-        <v>1568</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4162,15 +4162,15 @@
       </c>
       <c r="B45" s="4">
         <f>SUM(January:December!B45)</f>
-        <v>5022</v>
+        <v>6385</v>
       </c>
       <c r="C45" s="4">
         <f>SUM(January:December!C45)</f>
-        <v>2179</v>
+        <v>2649</v>
       </c>
       <c r="D45" s="4">
         <f>SUM(January:December!D45)</f>
-        <v>7201</v>
+        <v>9034</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4179,15 +4179,15 @@
       </c>
       <c r="B46" s="3">
         <f>SUM(January:December!B46)</f>
-        <v>9462</v>
+        <v>13715</v>
       </c>
       <c r="C46" s="3">
         <f>SUM(January:December!C46)</f>
-        <v>3642</v>
+        <v>4368</v>
       </c>
       <c r="D46" s="3">
         <f>SUM(January:December!D46)</f>
-        <v>13104</v>
+        <v>18083</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4196,15 +4196,15 @@
       </c>
       <c r="B47" s="4">
         <f>SUM(January:December!B47)</f>
-        <v>4823</v>
+        <v>6490</v>
       </c>
       <c r="C47" s="4">
         <f>SUM(January:December!C47)</f>
-        <v>960</v>
+        <v>1124</v>
       </c>
       <c r="D47" s="4">
         <f>SUM(January:December!D47)</f>
-        <v>5783</v>
+        <v>7614</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4213,15 +4213,15 @@
       </c>
       <c r="B48" s="3">
         <f>SUM(January:December!B48)</f>
-        <v>1963</v>
+        <v>2422</v>
       </c>
       <c r="C48" s="3">
         <f>SUM(January:December!C48)</f>
-        <v>1850</v>
+        <v>2129</v>
       </c>
       <c r="D48" s="3">
         <f>SUM(January:December!D48)</f>
-        <v>3813</v>
+        <v>4551</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4230,15 +4230,15 @@
       </c>
       <c r="B49" s="4">
         <f>SUM(January:December!B49)</f>
-        <v>11776</v>
+        <v>15406</v>
       </c>
       <c r="C49" s="4">
         <f>SUM(January:December!C49)</f>
-        <v>3735</v>
+        <v>4772</v>
       </c>
       <c r="D49" s="4">
         <f>SUM(January:December!D49)</f>
-        <v>15511</v>
+        <v>20178</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4247,15 +4247,15 @@
       </c>
       <c r="B50" s="3">
         <f>SUM(January:December!B50)</f>
-        <v>1363</v>
+        <v>1744</v>
       </c>
       <c r="C50" s="3">
         <f>SUM(January:December!C50)</f>
-        <v>513</v>
+        <v>610</v>
       </c>
       <c r="D50" s="3">
         <f>SUM(January:December!D50)</f>
-        <v>1876</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4264,15 +4264,15 @@
       </c>
       <c r="B51" s="4">
         <f>SUM(January:December!B51)</f>
-        <v>3496</v>
+        <v>4359</v>
       </c>
       <c r="C51" s="4">
         <f>SUM(January:December!C51)</f>
-        <v>2021</v>
+        <v>2334</v>
       </c>
       <c r="D51" s="4">
         <f>SUM(January:December!D51)</f>
-        <v>5517</v>
+        <v>6693</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4281,15 +4281,15 @@
       </c>
       <c r="B52" s="3">
         <f>SUM(January:December!B52)</f>
-        <v>318</v>
+        <v>385</v>
       </c>
       <c r="C52" s="3">
         <f>SUM(January:December!C52)</f>
-        <v>543</v>
+        <v>616</v>
       </c>
       <c r="D52" s="3">
         <f>SUM(January:December!D52)</f>
-        <v>861</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4298,15 +4298,15 @@
       </c>
       <c r="B53" s="4">
         <f>SUM(January:December!B53)</f>
-        <v>892</v>
+        <v>1141</v>
       </c>
       <c r="C53" s="4">
         <f>SUM(January:December!C53)</f>
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="D53" s="4">
         <f>SUM(January:December!D53)</f>
-        <v>1003</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4315,15 +4315,15 @@
       </c>
       <c r="B54" s="3">
         <f>SUM(January:December!B54)</f>
-        <v>1050</v>
+        <v>1683</v>
       </c>
       <c r="C54" s="3">
         <f>SUM(January:December!C54)</f>
-        <v>1683</v>
+        <v>1985</v>
       </c>
       <c r="D54" s="3">
         <f>SUM(January:December!D54)</f>
-        <v>2733</v>
+        <v>3668</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4332,15 +4332,15 @@
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>4004</v>
+        <v>5055</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>977</v>
+        <v>1152</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>4981</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4349,15 +4349,15 @@
       </c>
       <c r="B56" s="8">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>11565</v>
+        <v>11691</v>
       </c>
       <c r="C56" s="8">
         <f t="shared" ref="C56:D56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D56" s="8">
         <f t="shared" si="1"/>
-        <v>12158</v>
+        <v>12288</v>
       </c>
     </row>
   </sheetData>
@@ -6770,73 +6770,125 @@
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="B2" s="3">
+        <v>4694</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1251</v>
+      </c>
+      <c r="D2" s="3">
+        <v>5945</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="4">
+        <v>3114</v>
+      </c>
+      <c r="C3" s="4">
+        <v>501</v>
+      </c>
+      <c r="D3" s="4">
+        <v>3615</v>
+      </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="B4" s="3">
+        <v>7262</v>
+      </c>
+      <c r="C4" s="3">
+        <v>955</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8217</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="B5" s="4">
+        <v>151</v>
+      </c>
+      <c r="C5" s="4">
+        <v>19</v>
+      </c>
+      <c r="D5" s="4">
+        <v>170</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="B6" s="3">
+        <v>5368</v>
+      </c>
+      <c r="C6" s="3">
+        <v>891</v>
+      </c>
+      <c r="D6" s="3">
+        <v>6259</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="B7" s="4">
+        <v>534</v>
+      </c>
+      <c r="C7" s="4">
+        <v>409</v>
+      </c>
+      <c r="D7" s="4">
+        <v>943</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="B8" s="3">
+        <v>447</v>
+      </c>
+      <c r="C8" s="3">
+        <v>87</v>
+      </c>
+      <c r="D8" s="3">
+        <v>534</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="B9" s="4">
+        <v>244</v>
+      </c>
+      <c r="C9" s="4">
+        <v>47</v>
+      </c>
+      <c r="D9" s="4">
+        <v>291</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="3">
+        <v>30</v>
+      </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3">
+        <v>30</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -6850,113 +6902,197 @@
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="B12" s="5">
+        <v>59</v>
+      </c>
+      <c r="C12" s="5">
+        <v>4</v>
+      </c>
+      <c r="D12" s="5">
+        <v>63</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="6">
+        <v>140</v>
+      </c>
+      <c r="C13" s="6">
+        <v>44</v>
+      </c>
+      <c r="D13" s="6">
+        <v>184</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="5">
+        <v>597</v>
+      </c>
+      <c r="C14" s="5">
+        <v>97</v>
+      </c>
+      <c r="D14" s="5">
+        <v>694</v>
+      </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="B15" s="6">
+        <v>255</v>
+      </c>
+      <c r="C15" s="6">
+        <v>30</v>
+      </c>
+      <c r="D15" s="6">
+        <v>285</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="B16" s="3">
+        <v>209</v>
+      </c>
+      <c r="C16" s="3">
+        <v>52</v>
+      </c>
+      <c r="D16" s="3">
+        <v>261</v>
+      </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="B17" s="4">
+        <v>1397</v>
+      </c>
+      <c r="C17" s="4">
+        <v>557</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1954</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="B18" s="3">
+        <v>98</v>
+      </c>
+      <c r="C18" s="3">
+        <v>67</v>
+      </c>
+      <c r="D18" s="3">
+        <v>165</v>
+      </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
+      <c r="B19" s="4">
+        <v>1654</v>
+      </c>
+      <c r="C19" s="4">
+        <v>380</v>
+      </c>
+      <c r="D19" s="4">
+        <v>2034</v>
+      </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="B20" s="3">
+        <v>7</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3">
+        <v>8</v>
+      </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
+      <c r="B21" s="4">
+        <v>1618</v>
+      </c>
+      <c r="C21" s="4">
+        <v>510</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2128</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="B22" s="3">
+        <v>284</v>
+      </c>
+      <c r="C22" s="3">
+        <v>68</v>
+      </c>
+      <c r="D22" s="3">
+        <v>352</v>
+      </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="B23" s="4">
+        <v>1367</v>
+      </c>
+      <c r="C23" s="4">
+        <v>479</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1846</v>
+      </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="B24" s="3">
+        <v>11401</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1720</v>
+      </c>
+      <c r="D24" s="3">
+        <v>13121</v>
+      </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
+      <c r="B25" s="4">
+        <v>499</v>
+      </c>
+      <c r="C25" s="4">
+        <v>123</v>
+      </c>
+      <c r="D25" s="4">
+        <v>622</v>
+      </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
@@ -6970,129 +7106,221 @@
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
+      <c r="B27" s="4">
+        <v>451</v>
+      </c>
+      <c r="C27" s="4">
+        <v>225</v>
+      </c>
+      <c r="D27" s="4">
+        <v>676</v>
+      </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="B28" s="3">
+        <v>301</v>
+      </c>
+      <c r="C28" s="3">
+        <v>170</v>
+      </c>
+      <c r="D28" s="3">
+        <v>471</v>
+      </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="B29" s="4">
+        <v>2383</v>
+      </c>
+      <c r="C29" s="4">
+        <v>790</v>
+      </c>
+      <c r="D29" s="4">
+        <v>3173</v>
+      </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="B30" s="3">
+        <v>9</v>
+      </c>
+      <c r="C30" s="3">
+        <v>25</v>
+      </c>
+      <c r="D30" s="3">
+        <v>34</v>
+      </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+      <c r="B31" s="4">
+        <v>326</v>
+      </c>
+      <c r="C31" s="4">
+        <v>92</v>
+      </c>
+      <c r="D31" s="4">
+        <v>418</v>
+      </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="B32" s="3">
+        <v>1384</v>
+      </c>
+      <c r="C32" s="3">
+        <v>311</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1695</v>
+      </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="B33" s="4">
+        <v>906</v>
+      </c>
+      <c r="C33" s="4">
+        <v>295</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1201</v>
+      </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
+      <c r="B34" s="3">
+        <v>510</v>
+      </c>
+      <c r="C34" s="3">
+        <v>143</v>
+      </c>
+      <c r="D34" s="3">
+        <v>653</v>
+      </c>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
+      <c r="B35" s="4">
+        <v>4558</v>
+      </c>
+      <c r="C35" s="4">
+        <v>925</v>
+      </c>
+      <c r="D35" s="4">
+        <v>5483</v>
+      </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="B36" s="3">
+        <v>801</v>
+      </c>
+      <c r="C36" s="3">
+        <v>160</v>
+      </c>
+      <c r="D36" s="3">
+        <v>961</v>
+      </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
+      <c r="B37" s="4">
+        <v>3559</v>
+      </c>
+      <c r="C37" s="4">
+        <v>521</v>
+      </c>
+      <c r="D37" s="4">
+        <v>4080</v>
+      </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
+      <c r="B38" s="3">
+        <v>327</v>
+      </c>
+      <c r="C38" s="3">
+        <v>33</v>
+      </c>
+      <c r="D38" s="3">
+        <v>360</v>
+      </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
+      <c r="B39" s="4">
+        <v>77</v>
+      </c>
+      <c r="C39" s="4">
+        <v>139</v>
+      </c>
+      <c r="D39" s="4">
+        <v>216</v>
+      </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="7"/>
+      <c r="B40" s="7">
+        <v>102</v>
+      </c>
       <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+      <c r="D40" s="7">
+        <v>102</v>
+      </c>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="B41" s="8">
+        <v>22</v>
+      </c>
+      <c r="C41" s="8">
+        <v>4</v>
+      </c>
+      <c r="D41" s="8">
+        <v>26</v>
+      </c>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="7"/>
+      <c r="B42" s="7">
+        <v>2</v>
+      </c>
       <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
+      <c r="D42" s="7">
+        <v>2</v>
+      </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
@@ -7106,89 +7334,155 @@
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
+      <c r="B44" s="3">
+        <v>363</v>
+      </c>
+      <c r="C44" s="3">
+        <v>68</v>
+      </c>
+      <c r="D44" s="3">
+        <v>431</v>
+      </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
+      <c r="B45" s="4">
+        <v>1363</v>
+      </c>
+      <c r="C45" s="4">
+        <v>470</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1833</v>
+      </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
+      <c r="B46" s="3">
+        <v>4253</v>
+      </c>
+      <c r="C46" s="3">
+        <v>726</v>
+      </c>
+      <c r="D46" s="3">
+        <v>4979</v>
+      </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
+      <c r="B47" s="4">
+        <v>1667</v>
+      </c>
+      <c r="C47" s="4">
+        <v>164</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1831</v>
+      </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
+      <c r="B48" s="3">
+        <v>459</v>
+      </c>
+      <c r="C48" s="3">
+        <v>279</v>
+      </c>
+      <c r="D48" s="3">
+        <v>738</v>
+      </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
+      <c r="B49" s="4">
+        <v>3630</v>
+      </c>
+      <c r="C49" s="4">
+        <v>1037</v>
+      </c>
+      <c r="D49" s="4">
+        <v>4667</v>
+      </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
+      <c r="B50" s="3">
+        <v>381</v>
+      </c>
+      <c r="C50" s="3">
+        <v>97</v>
+      </c>
+      <c r="D50" s="3">
+        <v>478</v>
+      </c>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
+      <c r="B51" s="4">
+        <v>863</v>
+      </c>
+      <c r="C51" s="4">
+        <v>313</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1176</v>
+      </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
+      <c r="B52" s="3">
+        <v>67</v>
+      </c>
+      <c r="C52" s="3">
+        <v>73</v>
+      </c>
+      <c r="D52" s="3">
+        <v>140</v>
+      </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
+      <c r="B53" s="4">
+        <v>249</v>
+      </c>
+      <c r="C53" s="4">
+        <v>19</v>
+      </c>
+      <c r="D53" s="4">
+        <v>268</v>
+      </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
+      <c r="B54" s="3">
+        <v>633</v>
+      </c>
+      <c r="C54" s="3">
+        <v>302</v>
+      </c>
+      <c r="D54" s="3">
+        <v>935</v>
+      </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
@@ -7196,15 +7490,15 @@
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>0</v>
+        <v>1051</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7213,15 +7507,15 @@
       </c>
       <c r="B56" s="8">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="C56" s="8">
         <f t="shared" ref="C56:D56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D56" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/statistics_files/2026/2026_99_gc_sharing.xlsx
+++ b/statistics_files/2026/2026_99_gc_sharing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04F947F-A2C7-467F-80BB-93D427264548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654016C3-2EAA-4985-AF75-AD5E4A1A7A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -3431,15 +3431,15 @@
       </c>
       <c r="B2" s="3">
         <f>SUM(January:December!B2)</f>
-        <v>20717</v>
+        <v>26239</v>
       </c>
       <c r="C2" s="3">
         <f>SUM(January:December!C2)</f>
-        <v>7107</v>
+        <v>8466</v>
       </c>
       <c r="D2" s="3">
         <f>SUM(January:December!D2)</f>
-        <v>27824</v>
+        <v>34705</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3448,15 +3448,15 @@
       </c>
       <c r="B3" s="4">
         <f>SUM(January:December!B3)</f>
-        <v>13170</v>
+        <v>16623</v>
       </c>
       <c r="C3" s="4">
         <f>SUM(January:December!C3)</f>
-        <v>3000</v>
+        <v>3719</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(January:December!D3)</f>
-        <v>16170</v>
+        <v>20342</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3465,15 +3465,15 @@
       </c>
       <c r="B4" s="3">
         <f>SUM(January:December!B4)</f>
-        <v>37215</v>
+        <v>46538</v>
       </c>
       <c r="C4" s="3">
         <f>SUM(January:December!C4)</f>
-        <v>5813</v>
+        <v>7067</v>
       </c>
       <c r="D4" s="3">
         <f>SUM(January:December!D4)</f>
-        <v>43028</v>
+        <v>53605</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3482,15 +3482,15 @@
       </c>
       <c r="B5" s="4">
         <f>SUM(January:December!B5)</f>
-        <v>478</v>
+        <v>866</v>
       </c>
       <c r="C5" s="4">
         <f>SUM(January:December!C5)</f>
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="D5" s="4">
         <f>SUM(January:December!D5)</f>
-        <v>575</v>
+        <v>999</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3499,15 +3499,15 @@
       </c>
       <c r="B6" s="3">
         <f>SUM(January:December!B6)</f>
-        <v>25451</v>
+        <v>32106</v>
       </c>
       <c r="C6" s="3">
         <f>SUM(January:December!C6)</f>
-        <v>4985</v>
+        <v>5941</v>
       </c>
       <c r="D6" s="3">
         <f>SUM(January:December!D6)</f>
-        <v>30436</v>
+        <v>38047</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3516,15 +3516,15 @@
       </c>
       <c r="B7" s="4">
         <f>SUM(January:December!B7)</f>
-        <v>3363</v>
+        <v>3756</v>
       </c>
       <c r="C7" s="4">
         <f>SUM(January:December!C7)</f>
-        <v>1259</v>
+        <v>1499</v>
       </c>
       <c r="D7" s="4">
         <f>SUM(January:December!D7)</f>
-        <v>4622</v>
+        <v>5255</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3533,15 +3533,15 @@
       </c>
       <c r="B8" s="3">
         <f>SUM(January:December!B8)</f>
-        <v>2041</v>
+        <v>2573</v>
       </c>
       <c r="C8" s="3">
         <f>SUM(January:December!C8)</f>
-        <v>533</v>
+        <v>636</v>
       </c>
       <c r="D8" s="3">
         <f>SUM(January:December!D8)</f>
-        <v>2574</v>
+        <v>3209</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3550,15 +3550,15 @@
       </c>
       <c r="B9" s="4">
         <f>SUM(January:December!B9)</f>
-        <v>949</v>
+        <v>1297</v>
       </c>
       <c r="C9" s="4">
         <f>SUM(January:December!C9)</f>
-        <v>276</v>
+        <v>344</v>
       </c>
       <c r="D9" s="4">
         <f>SUM(January:December!D9)</f>
-        <v>1225</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="B10" s="3">
         <f>SUM(January:December!B10)</f>
-        <v>229</v>
+        <v>314</v>
       </c>
       <c r="C10" s="3">
         <f>SUM(January:December!C10)</f>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="D10" s="3">
         <f>SUM(January:December!D10)</f>
-        <v>232</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3601,15 +3601,15 @@
       </c>
       <c r="B12" s="5">
         <f>SUM(January:December!B12)</f>
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="C12" s="5">
         <f>SUM(January:December!C12)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D12" s="5">
         <f>SUM(January:December!D12)</f>
-        <v>182</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3618,15 +3618,15 @@
       </c>
       <c r="B13" s="6">
         <f>SUM(January:December!B13)</f>
-        <v>620</v>
+        <v>783</v>
       </c>
       <c r="C13" s="6">
         <f>SUM(January:December!C13)</f>
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="D13" s="6">
         <f>SUM(January:December!D13)</f>
-        <v>882</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3635,15 +3635,15 @@
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>3011</v>
+        <v>3609</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>644</v>
+        <v>751</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>3655</v>
+        <v>4360</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3652,15 +3652,15 @@
       </c>
       <c r="B15" s="6">
         <f>SUM(January:December!B15)</f>
-        <v>1269</v>
+        <v>1649</v>
       </c>
       <c r="C15" s="6">
         <f>SUM(January:December!C15)</f>
-        <v>219</v>
+        <v>275</v>
       </c>
       <c r="D15" s="6">
         <f>SUM(January:December!D15)</f>
-        <v>1488</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3669,15 +3669,15 @@
       </c>
       <c r="B16" s="3">
         <f>SUM(January:December!B16)</f>
-        <v>1121</v>
+        <v>1431</v>
       </c>
       <c r="C16" s="3">
         <f>SUM(January:December!C16)</f>
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="D16" s="3">
         <f>SUM(January:December!D16)</f>
-        <v>1432</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3686,15 +3686,15 @@
       </c>
       <c r="B17" s="4">
         <f>SUM(January:December!B17)</f>
-        <v>6105</v>
+        <v>8210</v>
       </c>
       <c r="C17" s="4">
         <f>SUM(January:December!C17)</f>
-        <v>3243</v>
+        <v>3913</v>
       </c>
       <c r="D17" s="4">
         <f>SUM(January:December!D17)</f>
-        <v>9348</v>
+        <v>12123</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3703,15 +3703,15 @@
       </c>
       <c r="B18" s="3">
         <f>SUM(January:December!B18)</f>
-        <v>463</v>
+        <v>572</v>
       </c>
       <c r="C18" s="3">
         <f>SUM(January:December!C18)</f>
-        <v>466</v>
+        <v>543</v>
       </c>
       <c r="D18" s="3">
         <f>SUM(January:December!D18)</f>
-        <v>929</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3720,15 +3720,15 @@
       </c>
       <c r="B19" s="4">
         <f>SUM(January:December!B19)</f>
-        <v>7856</v>
+        <v>10005</v>
       </c>
       <c r="C19" s="4">
         <f>SUM(January:December!C19)</f>
-        <v>2587</v>
+        <v>2987</v>
       </c>
       <c r="D19" s="4">
         <f>SUM(January:December!D19)</f>
-        <v>10443</v>
+        <v>12992</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3737,15 +3737,15 @@
       </c>
       <c r="B20" s="3">
         <f>SUM(January:December!B20)</f>
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C20" s="3">
         <f>SUM(January:December!C20)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" s="3">
         <f>SUM(January:December!D20)</f>
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3754,15 +3754,15 @@
       </c>
       <c r="B21" s="4">
         <f>SUM(January:December!B21)</f>
-        <v>7506</v>
+        <v>9437</v>
       </c>
       <c r="C21" s="4">
         <f>SUM(January:December!C21)</f>
-        <v>2468</v>
+        <v>2932</v>
       </c>
       <c r="D21" s="4">
         <f>SUM(January:December!D21)</f>
-        <v>9974</v>
+        <v>12369</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3771,15 +3771,15 @@
       </c>
       <c r="B22" s="3">
         <f>SUM(January:December!B22)</f>
-        <v>1258</v>
+        <v>1674</v>
       </c>
       <c r="C22" s="3">
         <f>SUM(January:December!C22)</f>
-        <v>445</v>
+        <v>524</v>
       </c>
       <c r="D22" s="3">
         <f>SUM(January:December!D22)</f>
-        <v>1703</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3788,15 +3788,15 @@
       </c>
       <c r="B23" s="4">
         <f>SUM(January:December!B23)</f>
-        <v>9926</v>
+        <v>12800</v>
       </c>
       <c r="C23" s="4">
         <f>SUM(January:December!C23)</f>
-        <v>3167</v>
+        <v>3751</v>
       </c>
       <c r="D23" s="4">
         <f>SUM(January:December!D23)</f>
-        <v>13093</v>
+        <v>16551</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3805,15 +3805,15 @@
       </c>
       <c r="B24" s="3">
         <f>SUM(January:December!B24)</f>
-        <v>49797</v>
+        <v>62248</v>
       </c>
       <c r="C24" s="3">
         <f>SUM(January:December!C24)</f>
-        <v>9023</v>
+        <v>10595</v>
       </c>
       <c r="D24" s="3">
         <f>SUM(January:December!D24)</f>
-        <v>58820</v>
+        <v>72843</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3822,15 +3822,15 @@
       </c>
       <c r="B25" s="4">
         <f>SUM(January:December!B25)</f>
-        <v>2105</v>
+        <v>2676</v>
       </c>
       <c r="C25" s="4">
         <f>SUM(January:December!C25)</f>
-        <v>801</v>
+        <v>952</v>
       </c>
       <c r="D25" s="4">
         <f>SUM(January:December!D25)</f>
-        <v>2906</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3856,15 +3856,15 @@
       </c>
       <c r="B27" s="4">
         <f>SUM(January:December!B27)</f>
-        <v>2070</v>
+        <v>2721</v>
       </c>
       <c r="C27" s="4">
         <f>SUM(January:December!C27)</f>
-        <v>988</v>
+        <v>1213</v>
       </c>
       <c r="D27" s="4">
         <f>SUM(January:December!D27)</f>
-        <v>3058</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3873,15 +3873,15 @@
       </c>
       <c r="B28" s="3">
         <f>SUM(January:December!B28)</f>
-        <v>1519</v>
+        <v>1991</v>
       </c>
       <c r="C28" s="3">
         <f>SUM(January:December!C28)</f>
-        <v>709</v>
+        <v>869</v>
       </c>
       <c r="D28" s="3">
         <f>SUM(January:December!D28)</f>
-        <v>2228</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3890,15 +3890,15 @@
       </c>
       <c r="B29" s="4">
         <f>SUM(January:December!B29)</f>
-        <v>9320</v>
+        <v>12420</v>
       </c>
       <c r="C29" s="4">
         <f>SUM(January:December!C29)</f>
-        <v>4127</v>
+        <v>5009</v>
       </c>
       <c r="D29" s="4">
         <f>SUM(January:December!D29)</f>
-        <v>13447</v>
+        <v>17429</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3907,15 +3907,15 @@
       </c>
       <c r="B30" s="3">
         <f>SUM(January:December!B30)</f>
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C30" s="3">
         <f>SUM(January:December!C30)</f>
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="D30" s="3">
         <f>SUM(January:December!D30)</f>
-        <v>217</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3924,15 +3924,15 @@
       </c>
       <c r="B31" s="4">
         <f>SUM(January:December!B31)</f>
-        <v>1660</v>
+        <v>1926</v>
       </c>
       <c r="C31" s="4">
         <f>SUM(January:December!C31)</f>
-        <v>597</v>
+        <v>691</v>
       </c>
       <c r="D31" s="4">
         <f>SUM(January:December!D31)</f>
-        <v>2257</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3941,15 +3941,15 @@
       </c>
       <c r="B32" s="3">
         <f>SUM(January:December!B32)</f>
-        <v>6125</v>
+        <v>7962</v>
       </c>
       <c r="C32" s="3">
         <f>SUM(January:December!C32)</f>
-        <v>2041</v>
+        <v>2376</v>
       </c>
       <c r="D32" s="3">
         <f>SUM(January:December!D32)</f>
-        <v>8166</v>
+        <v>10338</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3958,15 +3958,15 @@
       </c>
       <c r="B33" s="4">
         <f>SUM(January:December!B33)</f>
-        <v>3893</v>
+        <v>5433</v>
       </c>
       <c r="C33" s="4">
         <f>SUM(January:December!C33)</f>
-        <v>1748</v>
+        <v>2096</v>
       </c>
       <c r="D33" s="4">
         <f>SUM(January:December!D33)</f>
-        <v>5641</v>
+        <v>7529</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3975,15 +3975,15 @@
       </c>
       <c r="B34" s="3">
         <f>SUM(January:December!B34)</f>
-        <v>2278</v>
+        <v>2841</v>
       </c>
       <c r="C34" s="3">
         <f>SUM(January:December!C34)</f>
-        <v>867</v>
+        <v>1014</v>
       </c>
       <c r="D34" s="3">
         <f>SUM(January:December!D34)</f>
-        <v>3145</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3992,15 +3992,15 @@
       </c>
       <c r="B35" s="4">
         <f>SUM(January:December!B35)</f>
-        <v>23545</v>
+        <v>32327</v>
       </c>
       <c r="C35" s="4">
         <f>SUM(January:December!C35)</f>
-        <v>4883</v>
+        <v>5914</v>
       </c>
       <c r="D35" s="4">
         <f>SUM(January:December!D35)</f>
-        <v>28428</v>
+        <v>38241</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4009,15 +4009,15 @@
       </c>
       <c r="B36" s="3">
         <f>SUM(January:December!B36)</f>
-        <v>3702</v>
+        <v>4737</v>
       </c>
       <c r="C36" s="3">
         <f>SUM(January:December!C36)</f>
-        <v>850</v>
+        <v>1026</v>
       </c>
       <c r="D36" s="3">
         <f>SUM(January:December!D36)</f>
-        <v>4552</v>
+        <v>5763</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4026,15 +4026,15 @@
       </c>
       <c r="B37" s="4">
         <f>SUM(January:December!B37)</f>
-        <v>15043</v>
+        <v>19587</v>
       </c>
       <c r="C37" s="4">
         <f>SUM(January:December!C37)</f>
-        <v>2858</v>
+        <v>3408</v>
       </c>
       <c r="D37" s="4">
         <f>SUM(January:December!D37)</f>
-        <v>17901</v>
+        <v>22995</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4043,15 +4043,15 @@
       </c>
       <c r="B38" s="3">
         <f>SUM(January:December!B38)</f>
-        <v>1104</v>
+        <v>1678</v>
       </c>
       <c r="C38" s="3">
         <f>SUM(January:December!C38)</f>
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="D38" s="3">
         <f>SUM(January:December!D38)</f>
-        <v>1271</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4060,15 +4060,15 @@
       </c>
       <c r="B39" s="4">
         <f>SUM(January:December!B39)</f>
-        <v>454</v>
+        <v>628</v>
       </c>
       <c r="C39" s="4">
         <f>SUM(January:December!C39)</f>
-        <v>767</v>
+        <v>807</v>
       </c>
       <c r="D39" s="4">
         <f>SUM(January:December!D39)</f>
-        <v>1221</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4115,11 +4115,11 @@
       </c>
       <c r="C42" s="7">
         <f>SUM(January:December!C42)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D42" s="7">
         <f>SUM(January:December!D42)</f>
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4145,15 +4145,15 @@
       </c>
       <c r="B44" s="3">
         <f>SUM(January:December!B44)</f>
-        <v>1688</v>
+        <v>2196</v>
       </c>
       <c r="C44" s="3">
         <f>SUM(January:December!C44)</f>
-        <v>311</v>
+        <v>381</v>
       </c>
       <c r="D44" s="3">
         <f>SUM(January:December!D44)</f>
-        <v>1999</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4162,15 +4162,15 @@
       </c>
       <c r="B45" s="4">
         <f>SUM(January:December!B45)</f>
-        <v>6385</v>
+        <v>7968</v>
       </c>
       <c r="C45" s="4">
         <f>SUM(January:December!C45)</f>
-        <v>2649</v>
+        <v>3093</v>
       </c>
       <c r="D45" s="4">
         <f>SUM(January:December!D45)</f>
-        <v>9034</v>
+        <v>11061</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4179,15 +4179,15 @@
       </c>
       <c r="B46" s="3">
         <f>SUM(January:December!B46)</f>
-        <v>13715</v>
+        <v>19095</v>
       </c>
       <c r="C46" s="3">
         <f>SUM(January:December!C46)</f>
-        <v>4368</v>
+        <v>5150</v>
       </c>
       <c r="D46" s="3">
         <f>SUM(January:December!D46)</f>
-        <v>18083</v>
+        <v>24245</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4196,15 +4196,15 @@
       </c>
       <c r="B47" s="4">
         <f>SUM(January:December!B47)</f>
-        <v>6490</v>
+        <v>9057</v>
       </c>
       <c r="C47" s="4">
         <f>SUM(January:December!C47)</f>
-        <v>1124</v>
+        <v>1357</v>
       </c>
       <c r="D47" s="4">
         <f>SUM(January:December!D47)</f>
-        <v>7614</v>
+        <v>10414</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4213,15 +4213,15 @@
       </c>
       <c r="B48" s="3">
         <f>SUM(January:December!B48)</f>
-        <v>2422</v>
+        <v>3083</v>
       </c>
       <c r="C48" s="3">
         <f>SUM(January:December!C48)</f>
-        <v>2129</v>
+        <v>2380</v>
       </c>
       <c r="D48" s="3">
         <f>SUM(January:December!D48)</f>
-        <v>4551</v>
+        <v>5463</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4230,15 +4230,15 @@
       </c>
       <c r="B49" s="4">
         <f>SUM(January:December!B49)</f>
-        <v>15406</v>
+        <v>19831</v>
       </c>
       <c r="C49" s="4">
         <f>SUM(January:December!C49)</f>
-        <v>4772</v>
+        <v>5757</v>
       </c>
       <c r="D49" s="4">
         <f>SUM(January:December!D49)</f>
-        <v>20178</v>
+        <v>25588</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4247,15 +4247,15 @@
       </c>
       <c r="B50" s="3">
         <f>SUM(January:December!B50)</f>
-        <v>1744</v>
+        <v>2357</v>
       </c>
       <c r="C50" s="3">
         <f>SUM(January:December!C50)</f>
-        <v>610</v>
+        <v>717</v>
       </c>
       <c r="D50" s="3">
         <f>SUM(January:December!D50)</f>
-        <v>2354</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4264,15 +4264,15 @@
       </c>
       <c r="B51" s="4">
         <f>SUM(January:December!B51)</f>
-        <v>4359</v>
+        <v>5419</v>
       </c>
       <c r="C51" s="4">
         <f>SUM(January:December!C51)</f>
-        <v>2334</v>
+        <v>2675</v>
       </c>
       <c r="D51" s="4">
         <f>SUM(January:December!D51)</f>
-        <v>6693</v>
+        <v>8094</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4281,15 +4281,15 @@
       </c>
       <c r="B52" s="3">
         <f>SUM(January:December!B52)</f>
-        <v>385</v>
+        <v>518</v>
       </c>
       <c r="C52" s="3">
         <f>SUM(January:December!C52)</f>
-        <v>616</v>
+        <v>671</v>
       </c>
       <c r="D52" s="3">
         <f>SUM(January:December!D52)</f>
-        <v>1001</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4298,15 +4298,15 @@
       </c>
       <c r="B53" s="4">
         <f>SUM(January:December!B53)</f>
-        <v>1141</v>
+        <v>1270</v>
       </c>
       <c r="C53" s="4">
         <f>SUM(January:December!C53)</f>
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="D53" s="4">
         <f>SUM(January:December!D53)</f>
-        <v>1271</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4315,15 +4315,15 @@
       </c>
       <c r="B54" s="3">
         <f>SUM(January:December!B54)</f>
-        <v>1683</v>
+        <v>2235</v>
       </c>
       <c r="C54" s="3">
         <f>SUM(January:December!C54)</f>
-        <v>1985</v>
+        <v>2384</v>
       </c>
       <c r="D54" s="3">
         <f>SUM(January:December!D54)</f>
-        <v>3668</v>
+        <v>4619</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4332,15 +4332,15 @@
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>5055</v>
+        <v>6229</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>1152</v>
+        <v>1346</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>6207</v>
+        <v>7575</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4353,11 +4353,11 @@
       </c>
       <c r="C56" s="8">
         <f t="shared" ref="C56:D56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D56" s="8">
         <f t="shared" si="1"/>
-        <v>12288</v>
+        <v>12289</v>
       </c>
     </row>
   </sheetData>
@@ -7552,73 +7552,125 @@
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="B2" s="3">
+        <v>5522</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1359</v>
+      </c>
+      <c r="D2" s="3">
+        <v>6881</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="4">
+        <v>3453</v>
+      </c>
+      <c r="C3" s="4">
+        <v>719</v>
+      </c>
+      <c r="D3" s="4">
+        <v>4172</v>
+      </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="B4" s="3">
+        <v>9323</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1254</v>
+      </c>
+      <c r="D4" s="3">
+        <v>10577</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="B5" s="4">
+        <v>388</v>
+      </c>
+      <c r="C5" s="4">
+        <v>36</v>
+      </c>
+      <c r="D5" s="4">
+        <v>424</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="B6" s="3">
+        <v>6655</v>
+      </c>
+      <c r="C6" s="3">
+        <v>956</v>
+      </c>
+      <c r="D6" s="3">
+        <v>7611</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="B7" s="4">
+        <v>393</v>
+      </c>
+      <c r="C7" s="4">
+        <v>240</v>
+      </c>
+      <c r="D7" s="4">
+        <v>633</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="B8" s="3">
+        <v>532</v>
+      </c>
+      <c r="C8" s="3">
+        <v>103</v>
+      </c>
+      <c r="D8" s="3">
+        <v>635</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="B9" s="4">
+        <v>348</v>
+      </c>
+      <c r="C9" s="4">
+        <v>68</v>
+      </c>
+      <c r="D9" s="4">
+        <v>416</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="3">
+        <v>85</v>
+      </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3">
+        <v>85</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -7632,113 +7684,197 @@
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="B12" s="5">
+        <v>33</v>
+      </c>
+      <c r="C12" s="5">
+        <v>4</v>
+      </c>
+      <c r="D12" s="5">
+        <v>37</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="6">
+        <v>163</v>
+      </c>
+      <c r="C13" s="6">
+        <v>27</v>
+      </c>
+      <c r="D13" s="6">
+        <v>190</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="5">
+        <v>598</v>
+      </c>
+      <c r="C14" s="5">
+        <v>107</v>
+      </c>
+      <c r="D14" s="5">
+        <v>705</v>
+      </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="B15" s="6">
+        <v>380</v>
+      </c>
+      <c r="C15" s="6">
+        <v>56</v>
+      </c>
+      <c r="D15" s="6">
+        <v>436</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="B16" s="3">
+        <v>310</v>
+      </c>
+      <c r="C16" s="3">
+        <v>53</v>
+      </c>
+      <c r="D16" s="3">
+        <v>363</v>
+      </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="B17" s="4">
+        <v>2105</v>
+      </c>
+      <c r="C17" s="4">
+        <v>670</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2775</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="B18" s="3">
+        <v>109</v>
+      </c>
+      <c r="C18" s="3">
+        <v>77</v>
+      </c>
+      <c r="D18" s="3">
+        <v>186</v>
+      </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
+      <c r="B19" s="4">
+        <v>2149</v>
+      </c>
+      <c r="C19" s="4">
+        <v>400</v>
+      </c>
+      <c r="D19" s="4">
+        <v>2549</v>
+      </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="B20" s="3">
+        <v>3</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
+      <c r="B21" s="4">
+        <v>1931</v>
+      </c>
+      <c r="C21" s="4">
+        <v>464</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2395</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="B22" s="3">
+        <v>416</v>
+      </c>
+      <c r="C22" s="3">
+        <v>79</v>
+      </c>
+      <c r="D22" s="3">
+        <v>495</v>
+      </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="B23" s="4">
+        <v>2874</v>
+      </c>
+      <c r="C23" s="4">
+        <v>584</v>
+      </c>
+      <c r="D23" s="4">
+        <v>3458</v>
+      </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="B24" s="3">
+        <v>12451</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1572</v>
+      </c>
+      <c r="D24" s="3">
+        <v>14023</v>
+      </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
+      <c r="B25" s="4">
+        <v>571</v>
+      </c>
+      <c r="C25" s="4">
+        <v>151</v>
+      </c>
+      <c r="D25" s="4">
+        <v>722</v>
+      </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
@@ -7752,105 +7888,183 @@
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
+      <c r="B27" s="4">
+        <v>651</v>
+      </c>
+      <c r="C27" s="4">
+        <v>225</v>
+      </c>
+      <c r="D27" s="4">
+        <v>876</v>
+      </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="B28" s="3">
+        <v>472</v>
+      </c>
+      <c r="C28" s="3">
+        <v>160</v>
+      </c>
+      <c r="D28" s="3">
+        <v>632</v>
+      </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="B29" s="4">
+        <v>3100</v>
+      </c>
+      <c r="C29" s="4">
+        <v>882</v>
+      </c>
+      <c r="D29" s="4">
+        <v>3982</v>
+      </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="B30" s="3">
+        <v>7</v>
+      </c>
+      <c r="C30" s="3">
+        <v>20</v>
+      </c>
+      <c r="D30" s="3">
+        <v>27</v>
+      </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+      <c r="B31" s="4">
+        <v>266</v>
+      </c>
+      <c r="C31" s="4">
+        <v>94</v>
+      </c>
+      <c r="D31" s="4">
+        <v>360</v>
+      </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="B32" s="3">
+        <v>1837</v>
+      </c>
+      <c r="C32" s="3">
+        <v>335</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2172</v>
+      </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="B33" s="4">
+        <v>1540</v>
+      </c>
+      <c r="C33" s="4">
+        <v>348</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1888</v>
+      </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
+      <c r="B34" s="3">
+        <v>563</v>
+      </c>
+      <c r="C34" s="3">
+        <v>147</v>
+      </c>
+      <c r="D34" s="3">
+        <v>710</v>
+      </c>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
+      <c r="B35" s="4">
+        <v>8782</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1031</v>
+      </c>
+      <c r="D35" s="4">
+        <v>9813</v>
+      </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="B36" s="3">
+        <v>1035</v>
+      </c>
+      <c r="C36" s="3">
+        <v>176</v>
+      </c>
+      <c r="D36" s="3">
+        <v>1211</v>
+      </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
+      <c r="B37" s="4">
+        <v>4544</v>
+      </c>
+      <c r="C37" s="4">
+        <v>550</v>
+      </c>
+      <c r="D37" s="4">
+        <v>5094</v>
+      </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
+      <c r="B38" s="3">
+        <v>574</v>
+      </c>
+      <c r="C38" s="3">
+        <v>78</v>
+      </c>
+      <c r="D38" s="3">
+        <v>652</v>
+      </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
+      <c r="B39" s="4">
+        <v>174</v>
+      </c>
+      <c r="C39" s="4">
+        <v>40</v>
+      </c>
+      <c r="D39" s="4">
+        <v>214</v>
+      </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
@@ -7873,8 +8087,12 @@
         <v>44</v>
       </c>
       <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
+      <c r="C42" s="7">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
@@ -7888,89 +8106,155 @@
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
+      <c r="B44" s="3">
+        <v>508</v>
+      </c>
+      <c r="C44" s="3">
+        <v>70</v>
+      </c>
+      <c r="D44" s="3">
+        <v>578</v>
+      </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
+      <c r="B45" s="4">
+        <v>1583</v>
+      </c>
+      <c r="C45" s="4">
+        <v>444</v>
+      </c>
+      <c r="D45" s="4">
+        <v>2027</v>
+      </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
+      <c r="B46" s="3">
+        <v>5380</v>
+      </c>
+      <c r="C46" s="3">
+        <v>782</v>
+      </c>
+      <c r="D46" s="3">
+        <v>6162</v>
+      </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
+      <c r="B47" s="4">
+        <v>2567</v>
+      </c>
+      <c r="C47" s="4">
+        <v>233</v>
+      </c>
+      <c r="D47" s="4">
+        <v>2800</v>
+      </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
+      <c r="B48" s="3">
+        <v>661</v>
+      </c>
+      <c r="C48" s="3">
+        <v>251</v>
+      </c>
+      <c r="D48" s="3">
+        <v>912</v>
+      </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
+      <c r="B49" s="4">
+        <v>4425</v>
+      </c>
+      <c r="C49" s="4">
+        <v>985</v>
+      </c>
+      <c r="D49" s="4">
+        <v>5410</v>
+      </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
+      <c r="B50" s="3">
+        <v>613</v>
+      </c>
+      <c r="C50" s="3">
+        <v>107</v>
+      </c>
+      <c r="D50" s="3">
+        <v>720</v>
+      </c>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
+      <c r="B51" s="4">
+        <v>1060</v>
+      </c>
+      <c r="C51" s="4">
+        <v>341</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1401</v>
+      </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
+      <c r="B52" s="3">
+        <v>133</v>
+      </c>
+      <c r="C52" s="3">
+        <v>55</v>
+      </c>
+      <c r="D52" s="3">
+        <v>188</v>
+      </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
+      <c r="B53" s="4">
+        <v>129</v>
+      </c>
+      <c r="C53" s="4">
+        <v>27</v>
+      </c>
+      <c r="D53" s="4">
+        <v>156</v>
+      </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
+      <c r="B54" s="3">
+        <v>552</v>
+      </c>
+      <c r="C54" s="3">
+        <v>399</v>
+      </c>
+      <c r="D54" s="3">
+        <v>951</v>
+      </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
@@ -7978,15 +8262,15 @@
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>0</v>
+        <v>1174</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7999,11 +8283,11 @@
       </c>
       <c r="C56" s="8">
         <f t="shared" ref="C56:D56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/statistics_files/2026/2026_99_gc_sharing.xlsx
+++ b/statistics_files/2026/2026_99_gc_sharing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654016C3-2EAA-4985-AF75-AD5E4A1A7A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF4DBFF-D719-45C8-A435-470FF614D279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -3431,15 +3431,15 @@
       </c>
       <c r="B2" s="3">
         <f>SUM(January:December!B2)</f>
-        <v>26239</v>
+        <v>31377</v>
       </c>
       <c r="C2" s="3">
         <f>SUM(January:December!C2)</f>
-        <v>8466</v>
+        <v>9925</v>
       </c>
       <c r="D2" s="3">
         <f>SUM(January:December!D2)</f>
-        <v>34705</v>
+        <v>41302</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3448,15 +3448,15 @@
       </c>
       <c r="B3" s="4">
         <f>SUM(January:December!B3)</f>
-        <v>16623</v>
+        <v>20066</v>
       </c>
       <c r="C3" s="4">
         <f>SUM(January:December!C3)</f>
-        <v>3719</v>
+        <v>4490</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(January:December!D3)</f>
-        <v>20342</v>
+        <v>24556</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3465,15 +3465,15 @@
       </c>
       <c r="B4" s="3">
         <f>SUM(January:December!B4)</f>
-        <v>46538</v>
+        <v>55232</v>
       </c>
       <c r="C4" s="3">
         <f>SUM(January:December!C4)</f>
-        <v>7067</v>
+        <v>8337</v>
       </c>
       <c r="D4" s="3">
         <f>SUM(January:December!D4)</f>
-        <v>53605</v>
+        <v>63569</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3482,15 +3482,15 @@
       </c>
       <c r="B5" s="4">
         <f>SUM(January:December!B5)</f>
-        <v>866</v>
+        <v>1116</v>
       </c>
       <c r="C5" s="4">
         <f>SUM(January:December!C5)</f>
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="D5" s="4">
         <f>SUM(January:December!D5)</f>
-        <v>999</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3499,15 +3499,15 @@
       </c>
       <c r="B6" s="3">
         <f>SUM(January:December!B6)</f>
-        <v>32106</v>
+        <v>38893</v>
       </c>
       <c r="C6" s="3">
         <f>SUM(January:December!C6)</f>
-        <v>5941</v>
+        <v>6861</v>
       </c>
       <c r="D6" s="3">
         <f>SUM(January:December!D6)</f>
-        <v>38047</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3516,15 +3516,15 @@
       </c>
       <c r="B7" s="4">
         <f>SUM(January:December!B7)</f>
-        <v>3756</v>
+        <v>4203</v>
       </c>
       <c r="C7" s="4">
         <f>SUM(January:December!C7)</f>
-        <v>1499</v>
+        <v>1772</v>
       </c>
       <c r="D7" s="4">
         <f>SUM(January:December!D7)</f>
-        <v>5255</v>
+        <v>5975</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3533,15 +3533,15 @@
       </c>
       <c r="B8" s="3">
         <f>SUM(January:December!B8)</f>
-        <v>2573</v>
+        <v>2979</v>
       </c>
       <c r="C8" s="3">
         <f>SUM(January:December!C8)</f>
-        <v>636</v>
+        <v>801</v>
       </c>
       <c r="D8" s="3">
         <f>SUM(January:December!D8)</f>
-        <v>3209</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3550,15 +3550,15 @@
       </c>
       <c r="B9" s="4">
         <f>SUM(January:December!B9)</f>
-        <v>1297</v>
+        <v>1697</v>
       </c>
       <c r="C9" s="4">
         <f>SUM(January:December!C9)</f>
-        <v>344</v>
+        <v>420</v>
       </c>
       <c r="D9" s="4">
         <f>SUM(January:December!D9)</f>
-        <v>1641</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3567,15 +3567,15 @@
       </c>
       <c r="B10" s="3">
         <f>SUM(January:December!B10)</f>
-        <v>314</v>
+        <v>377</v>
       </c>
       <c r="C10" s="3">
         <f>SUM(January:December!C10)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" s="3">
         <f>SUM(January:December!D10)</f>
-        <v>317</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3601,15 +3601,15 @@
       </c>
       <c r="B12" s="5">
         <f>SUM(January:December!B12)</f>
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="C12" s="5">
         <f>SUM(January:December!C12)</f>
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D12" s="5">
         <f>SUM(January:December!D12)</f>
-        <v>219</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3618,15 +3618,15 @@
       </c>
       <c r="B13" s="6">
         <f>SUM(January:December!B13)</f>
-        <v>783</v>
+        <v>921</v>
       </c>
       <c r="C13" s="6">
         <f>SUM(January:December!C13)</f>
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="D13" s="6">
         <f>SUM(January:December!D13)</f>
-        <v>1072</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3635,15 +3635,15 @@
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>3609</v>
+        <v>4233</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>751</v>
+        <v>867</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>4360</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3652,15 +3652,15 @@
       </c>
       <c r="B15" s="6">
         <f>SUM(January:December!B15)</f>
-        <v>1649</v>
+        <v>1977</v>
       </c>
       <c r="C15" s="6">
         <f>SUM(January:December!C15)</f>
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="D15" s="6">
         <f>SUM(January:December!D15)</f>
-        <v>1924</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3669,15 +3669,15 @@
       </c>
       <c r="B16" s="3">
         <f>SUM(January:December!B16)</f>
-        <v>1431</v>
+        <v>1713</v>
       </c>
       <c r="C16" s="3">
         <f>SUM(January:December!C16)</f>
-        <v>364</v>
+        <v>413</v>
       </c>
       <c r="D16" s="3">
         <f>SUM(January:December!D16)</f>
-        <v>1795</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3686,15 +3686,15 @@
       </c>
       <c r="B17" s="4">
         <f>SUM(January:December!B17)</f>
-        <v>8210</v>
+        <v>10063</v>
       </c>
       <c r="C17" s="4">
         <f>SUM(January:December!C17)</f>
-        <v>3913</v>
+        <v>4526</v>
       </c>
       <c r="D17" s="4">
         <f>SUM(January:December!D17)</f>
-        <v>12123</v>
+        <v>14589</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3703,15 +3703,15 @@
       </c>
       <c r="B18" s="3">
         <f>SUM(January:December!B18)</f>
-        <v>572</v>
+        <v>705</v>
       </c>
       <c r="C18" s="3">
         <f>SUM(January:December!C18)</f>
-        <v>543</v>
+        <v>595</v>
       </c>
       <c r="D18" s="3">
         <f>SUM(January:December!D18)</f>
-        <v>1115</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3720,15 +3720,15 @@
       </c>
       <c r="B19" s="4">
         <f>SUM(January:December!B19)</f>
-        <v>10005</v>
+        <v>12121</v>
       </c>
       <c r="C19" s="4">
         <f>SUM(January:December!C19)</f>
-        <v>2987</v>
+        <v>3550</v>
       </c>
       <c r="D19" s="4">
         <f>SUM(January:December!D19)</f>
-        <v>12992</v>
+        <v>15671</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="B20" s="3">
         <f>SUM(January:December!B20)</f>
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C20" s="3">
         <f>SUM(January:December!C20)</f>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="D20" s="3">
         <f>SUM(January:December!D20)</f>
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3754,15 +3754,15 @@
       </c>
       <c r="B21" s="4">
         <f>SUM(January:December!B21)</f>
-        <v>9437</v>
+        <v>11134</v>
       </c>
       <c r="C21" s="4">
         <f>SUM(January:December!C21)</f>
-        <v>2932</v>
+        <v>3481</v>
       </c>
       <c r="D21" s="4">
         <f>SUM(January:December!D21)</f>
-        <v>12369</v>
+        <v>14615</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3771,15 +3771,15 @@
       </c>
       <c r="B22" s="3">
         <f>SUM(January:December!B22)</f>
-        <v>1674</v>
+        <v>2046</v>
       </c>
       <c r="C22" s="3">
         <f>SUM(January:December!C22)</f>
-        <v>524</v>
+        <v>586</v>
       </c>
       <c r="D22" s="3">
         <f>SUM(January:December!D22)</f>
-        <v>2198</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3788,15 +3788,15 @@
       </c>
       <c r="B23" s="4">
         <f>SUM(January:December!B23)</f>
-        <v>12800</v>
+        <v>15807</v>
       </c>
       <c r="C23" s="4">
         <f>SUM(January:December!C23)</f>
-        <v>3751</v>
+        <v>4489</v>
       </c>
       <c r="D23" s="4">
         <f>SUM(January:December!D23)</f>
-        <v>16551</v>
+        <v>20296</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3805,15 +3805,15 @@
       </c>
       <c r="B24" s="3">
         <f>SUM(January:December!B24)</f>
-        <v>62248</v>
+        <v>74704</v>
       </c>
       <c r="C24" s="3">
         <f>SUM(January:December!C24)</f>
-        <v>10595</v>
+        <v>12206</v>
       </c>
       <c r="D24" s="3">
         <f>SUM(January:December!D24)</f>
-        <v>72843</v>
+        <v>86910</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3822,15 +3822,15 @@
       </c>
       <c r="B25" s="4">
         <f>SUM(January:December!B25)</f>
-        <v>2676</v>
+        <v>3152</v>
       </c>
       <c r="C25" s="4">
         <f>SUM(January:December!C25)</f>
-        <v>952</v>
+        <v>1055</v>
       </c>
       <c r="D25" s="4">
         <f>SUM(January:December!D25)</f>
-        <v>3628</v>
+        <v>4207</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3856,15 +3856,15 @@
       </c>
       <c r="B27" s="4">
         <f>SUM(January:December!B27)</f>
-        <v>2721</v>
+        <v>3241</v>
       </c>
       <c r="C27" s="4">
         <f>SUM(January:December!C27)</f>
-        <v>1213</v>
+        <v>1448</v>
       </c>
       <c r="D27" s="4">
         <f>SUM(January:December!D27)</f>
-        <v>3934</v>
+        <v>4689</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3873,15 +3873,15 @@
       </c>
       <c r="B28" s="3">
         <f>SUM(January:December!B28)</f>
-        <v>1991</v>
+        <v>2336</v>
       </c>
       <c r="C28" s="3">
         <f>SUM(January:December!C28)</f>
-        <v>869</v>
+        <v>1052</v>
       </c>
       <c r="D28" s="3">
         <f>SUM(January:December!D28)</f>
-        <v>2860</v>
+        <v>3388</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3890,15 +3890,15 @@
       </c>
       <c r="B29" s="4">
         <f>SUM(January:December!B29)</f>
-        <v>12420</v>
+        <v>15015</v>
       </c>
       <c r="C29" s="4">
         <f>SUM(January:December!C29)</f>
-        <v>5009</v>
+        <v>5853</v>
       </c>
       <c r="D29" s="4">
         <f>SUM(January:December!D29)</f>
-        <v>17429</v>
+        <v>20868</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3907,15 +3907,15 @@
       </c>
       <c r="B30" s="3">
         <f>SUM(January:December!B30)</f>
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C30" s="3">
         <f>SUM(January:December!C30)</f>
-        <v>175</v>
+        <v>263</v>
       </c>
       <c r="D30" s="3">
         <f>SUM(January:December!D30)</f>
-        <v>244</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3924,15 +3924,15 @@
       </c>
       <c r="B31" s="4">
         <f>SUM(January:December!B31)</f>
-        <v>1926</v>
+        <v>2132</v>
       </c>
       <c r="C31" s="4">
         <f>SUM(January:December!C31)</f>
-        <v>691</v>
+        <v>803</v>
       </c>
       <c r="D31" s="4">
         <f>SUM(January:December!D31)</f>
-        <v>2617</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3941,15 +3941,15 @@
       </c>
       <c r="B32" s="3">
         <f>SUM(January:December!B32)</f>
-        <v>7962</v>
+        <v>9573</v>
       </c>
       <c r="C32" s="3">
         <f>SUM(January:December!C32)</f>
-        <v>2376</v>
+        <v>2825</v>
       </c>
       <c r="D32" s="3">
         <f>SUM(January:December!D32)</f>
-        <v>10338</v>
+        <v>12398</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3958,15 +3958,15 @@
       </c>
       <c r="B33" s="4">
         <f>SUM(January:December!B33)</f>
-        <v>5433</v>
+        <v>6628</v>
       </c>
       <c r="C33" s="4">
         <f>SUM(January:December!C33)</f>
-        <v>2096</v>
+        <v>2419</v>
       </c>
       <c r="D33" s="4">
         <f>SUM(January:December!D33)</f>
-        <v>7529</v>
+        <v>9047</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3975,15 +3975,15 @@
       </c>
       <c r="B34" s="3">
         <f>SUM(January:December!B34)</f>
-        <v>2841</v>
+        <v>3476</v>
       </c>
       <c r="C34" s="3">
         <f>SUM(January:December!C34)</f>
-        <v>1014</v>
+        <v>1197</v>
       </c>
       <c r="D34" s="3">
         <f>SUM(January:December!D34)</f>
-        <v>3855</v>
+        <v>4673</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3992,15 +3992,15 @@
       </c>
       <c r="B35" s="4">
         <f>SUM(January:December!B35)</f>
-        <v>32327</v>
+        <v>39622</v>
       </c>
       <c r="C35" s="4">
         <f>SUM(January:December!C35)</f>
-        <v>5914</v>
+        <v>6946</v>
       </c>
       <c r="D35" s="4">
         <f>SUM(January:December!D35)</f>
-        <v>38241</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4009,15 +4009,15 @@
       </c>
       <c r="B36" s="3">
         <f>SUM(January:December!B36)</f>
-        <v>4737</v>
+        <v>5650</v>
       </c>
       <c r="C36" s="3">
         <f>SUM(January:December!C36)</f>
-        <v>1026</v>
+        <v>1203</v>
       </c>
       <c r="D36" s="3">
         <f>SUM(January:December!D36)</f>
-        <v>5763</v>
+        <v>6853</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4026,15 +4026,15 @@
       </c>
       <c r="B37" s="4">
         <f>SUM(January:December!B37)</f>
-        <v>19587</v>
+        <v>23812</v>
       </c>
       <c r="C37" s="4">
         <f>SUM(January:December!C37)</f>
-        <v>3408</v>
+        <v>4054</v>
       </c>
       <c r="D37" s="4">
         <f>SUM(January:December!D37)</f>
-        <v>22995</v>
+        <v>27866</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4043,15 +4043,15 @@
       </c>
       <c r="B38" s="3">
         <f>SUM(January:December!B38)</f>
-        <v>1678</v>
+        <v>2082</v>
       </c>
       <c r="C38" s="3">
         <f>SUM(January:December!C38)</f>
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="D38" s="3">
         <f>SUM(January:December!D38)</f>
-        <v>1923</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4060,15 +4060,15 @@
       </c>
       <c r="B39" s="4">
         <f>SUM(January:December!B39)</f>
-        <v>628</v>
+        <v>735</v>
       </c>
       <c r="C39" s="4">
         <f>SUM(January:December!C39)</f>
-        <v>807</v>
+        <v>936</v>
       </c>
       <c r="D39" s="4">
         <f>SUM(January:December!D39)</f>
-        <v>1435</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4145,15 +4145,15 @@
       </c>
       <c r="B44" s="3">
         <f>SUM(January:December!B44)</f>
-        <v>2196</v>
+        <v>2623</v>
       </c>
       <c r="C44" s="3">
         <f>SUM(January:December!C44)</f>
-        <v>381</v>
+        <v>436</v>
       </c>
       <c r="D44" s="3">
         <f>SUM(January:December!D44)</f>
-        <v>2577</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4162,15 +4162,15 @@
       </c>
       <c r="B45" s="4">
         <f>SUM(January:December!B45)</f>
-        <v>7968</v>
+        <v>9678</v>
       </c>
       <c r="C45" s="4">
         <f>SUM(January:December!C45)</f>
-        <v>3093</v>
+        <v>3599</v>
       </c>
       <c r="D45" s="4">
         <f>SUM(January:December!D45)</f>
-        <v>11061</v>
+        <v>13277</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4179,15 +4179,15 @@
       </c>
       <c r="B46" s="3">
         <f>SUM(January:December!B46)</f>
-        <v>19095</v>
+        <v>23105</v>
       </c>
       <c r="C46" s="3">
         <f>SUM(January:December!C46)</f>
-        <v>5150</v>
+        <v>5887</v>
       </c>
       <c r="D46" s="3">
         <f>SUM(January:December!D46)</f>
-        <v>24245</v>
+        <v>28992</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4196,15 +4196,15 @@
       </c>
       <c r="B47" s="4">
         <f>SUM(January:December!B47)</f>
-        <v>9057</v>
+        <v>11269</v>
       </c>
       <c r="C47" s="4">
         <f>SUM(January:December!C47)</f>
-        <v>1357</v>
+        <v>1581</v>
       </c>
       <c r="D47" s="4">
         <f>SUM(January:December!D47)</f>
-        <v>10414</v>
+        <v>12850</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4213,15 +4213,15 @@
       </c>
       <c r="B48" s="3">
         <f>SUM(January:December!B48)</f>
-        <v>3083</v>
+        <v>3820</v>
       </c>
       <c r="C48" s="3">
         <f>SUM(January:December!C48)</f>
-        <v>2380</v>
+        <v>2673</v>
       </c>
       <c r="D48" s="3">
         <f>SUM(January:December!D48)</f>
-        <v>5463</v>
+        <v>6493</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4230,15 +4230,15 @@
       </c>
       <c r="B49" s="4">
         <f>SUM(January:December!B49)</f>
-        <v>19831</v>
+        <v>23548</v>
       </c>
       <c r="C49" s="4">
         <f>SUM(January:December!C49)</f>
-        <v>5757</v>
+        <v>6699</v>
       </c>
       <c r="D49" s="4">
         <f>SUM(January:December!D49)</f>
-        <v>25588</v>
+        <v>30247</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4247,15 +4247,15 @@
       </c>
       <c r="B50" s="3">
         <f>SUM(January:December!B50)</f>
-        <v>2357</v>
+        <v>2714</v>
       </c>
       <c r="C50" s="3">
         <f>SUM(January:December!C50)</f>
-        <v>717</v>
+        <v>810</v>
       </c>
       <c r="D50" s="3">
         <f>SUM(January:December!D50)</f>
-        <v>3074</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4264,15 +4264,15 @@
       </c>
       <c r="B51" s="4">
         <f>SUM(January:December!B51)</f>
-        <v>5419</v>
+        <v>6234</v>
       </c>
       <c r="C51" s="4">
         <f>SUM(January:December!C51)</f>
-        <v>2675</v>
+        <v>2994</v>
       </c>
       <c r="D51" s="4">
         <f>SUM(January:December!D51)</f>
-        <v>8094</v>
+        <v>9228</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4281,15 +4281,15 @@
       </c>
       <c r="B52" s="3">
         <f>SUM(January:December!B52)</f>
-        <v>518</v>
+        <v>626</v>
       </c>
       <c r="C52" s="3">
         <f>SUM(January:December!C52)</f>
-        <v>671</v>
+        <v>697</v>
       </c>
       <c r="D52" s="3">
         <f>SUM(January:December!D52)</f>
-        <v>1189</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4298,15 +4298,15 @@
       </c>
       <c r="B53" s="4">
         <f>SUM(January:December!B53)</f>
-        <v>1270</v>
+        <v>1367</v>
       </c>
       <c r="C53" s="4">
         <f>SUM(January:December!C53)</f>
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="D53" s="4">
         <f>SUM(January:December!D53)</f>
-        <v>1427</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4315,15 +4315,15 @@
       </c>
       <c r="B54" s="3">
         <f>SUM(January:December!B54)</f>
-        <v>2235</v>
+        <v>2600</v>
       </c>
       <c r="C54" s="3">
         <f>SUM(January:December!C54)</f>
-        <v>2384</v>
+        <v>2688</v>
       </c>
       <c r="D54" s="3">
         <f>SUM(January:December!D54)</f>
-        <v>4619</v>
+        <v>5288</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4332,15 +4332,15 @@
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>6229</v>
+        <v>7363</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>1346</v>
+        <v>1556</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>7575</v>
+        <v>8919</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8324,73 +8324,127 @@
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="B2" s="3">
+        <v>5138</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1459</v>
+      </c>
+      <c r="D2" s="3">
+        <v>6597</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="4">
+        <v>3443</v>
+      </c>
+      <c r="C3" s="4">
+        <v>771</v>
+      </c>
+      <c r="D3" s="4">
+        <v>4214</v>
+      </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="B4" s="3">
+        <v>8694</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1270</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9964</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="B5" s="4">
+        <v>250</v>
+      </c>
+      <c r="C5" s="4">
+        <v>31</v>
+      </c>
+      <c r="D5" s="4">
+        <v>281</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="B6" s="3">
+        <v>6787</v>
+      </c>
+      <c r="C6" s="3">
+        <v>920</v>
+      </c>
+      <c r="D6" s="3">
+        <v>7707</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="B7" s="4">
+        <v>447</v>
+      </c>
+      <c r="C7" s="4">
+        <v>273</v>
+      </c>
+      <c r="D7" s="4">
+        <v>720</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="B8" s="3">
+        <v>406</v>
+      </c>
+      <c r="C8" s="3">
+        <v>165</v>
+      </c>
+      <c r="D8" s="3">
+        <v>571</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="B9" s="4">
+        <v>400</v>
+      </c>
+      <c r="C9" s="4">
+        <v>76</v>
+      </c>
+      <c r="D9" s="4">
+        <v>476</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="B10" s="3">
+        <v>63</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3">
+        <v>65</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -8404,113 +8458,195 @@
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="B12" s="5">
+        <v>44</v>
+      </c>
+      <c r="C12" s="5">
+        <v>8</v>
+      </c>
+      <c r="D12" s="5">
+        <v>52</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="6">
+        <v>138</v>
+      </c>
+      <c r="C13" s="6">
+        <v>34</v>
+      </c>
+      <c r="D13" s="6">
+        <v>172</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="5">
+        <v>624</v>
+      </c>
+      <c r="C14" s="5">
+        <v>116</v>
+      </c>
+      <c r="D14" s="5">
+        <v>740</v>
+      </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="B15" s="6">
+        <v>328</v>
+      </c>
+      <c r="C15" s="6">
+        <v>52</v>
+      </c>
+      <c r="D15" s="6">
+        <v>380</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="B16" s="3">
+        <v>282</v>
+      </c>
+      <c r="C16" s="3">
+        <v>49</v>
+      </c>
+      <c r="D16" s="3">
+        <v>331</v>
+      </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="B17" s="4">
+        <v>1853</v>
+      </c>
+      <c r="C17" s="4">
+        <v>613</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2466</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="B18" s="3">
+        <v>133</v>
+      </c>
+      <c r="C18" s="3">
+        <v>52</v>
+      </c>
+      <c r="D18" s="3">
+        <v>185</v>
+      </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
+      <c r="B19" s="4">
+        <v>2116</v>
+      </c>
+      <c r="C19" s="4">
+        <v>563</v>
+      </c>
+      <c r="D19" s="4">
+        <v>2679</v>
+      </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3"/>
+      <c r="B20" s="3">
+        <v>12</v>
+      </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3">
+        <v>12</v>
+      </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
+      <c r="B21" s="4">
+        <v>1697</v>
+      </c>
+      <c r="C21" s="4">
+        <v>549</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2246</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="B22" s="3">
+        <v>372</v>
+      </c>
+      <c r="C22" s="3">
+        <v>62</v>
+      </c>
+      <c r="D22" s="3">
+        <v>434</v>
+      </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="B23" s="4">
+        <v>3007</v>
+      </c>
+      <c r="C23" s="4">
+        <v>738</v>
+      </c>
+      <c r="D23" s="4">
+        <v>3745</v>
+      </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="B24" s="3">
+        <v>12456</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1611</v>
+      </c>
+      <c r="D24" s="3">
+        <v>14067</v>
+      </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
+      <c r="B25" s="4">
+        <v>476</v>
+      </c>
+      <c r="C25" s="4">
+        <v>103</v>
+      </c>
+      <c r="D25" s="4">
+        <v>579</v>
+      </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
@@ -8524,105 +8660,183 @@
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
+      <c r="B27" s="4">
+        <v>520</v>
+      </c>
+      <c r="C27" s="4">
+        <v>235</v>
+      </c>
+      <c r="D27" s="4">
+        <v>755</v>
+      </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="B28" s="3">
+        <v>345</v>
+      </c>
+      <c r="C28" s="3">
+        <v>183</v>
+      </c>
+      <c r="D28" s="3">
+        <v>528</v>
+      </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="B29" s="4">
+        <v>2595</v>
+      </c>
+      <c r="C29" s="4">
+        <v>844</v>
+      </c>
+      <c r="D29" s="4">
+        <v>3439</v>
+      </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="B30" s="3">
+        <v>16</v>
+      </c>
+      <c r="C30" s="3">
+        <v>88</v>
+      </c>
+      <c r="D30" s="3">
+        <v>104</v>
+      </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+      <c r="B31" s="4">
+        <v>206</v>
+      </c>
+      <c r="C31" s="4">
+        <v>112</v>
+      </c>
+      <c r="D31" s="4">
+        <v>318</v>
+      </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="B32" s="3">
+        <v>1611</v>
+      </c>
+      <c r="C32" s="3">
+        <v>449</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2060</v>
+      </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="B33" s="4">
+        <v>1195</v>
+      </c>
+      <c r="C33" s="4">
+        <v>323</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1518</v>
+      </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
+      <c r="B34" s="3">
+        <v>635</v>
+      </c>
+      <c r="C34" s="3">
+        <v>183</v>
+      </c>
+      <c r="D34" s="3">
+        <v>818</v>
+      </c>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
+      <c r="B35" s="4">
+        <v>7295</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1032</v>
+      </c>
+      <c r="D35" s="4">
+        <v>8327</v>
+      </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="B36" s="3">
+        <v>913</v>
+      </c>
+      <c r="C36" s="3">
+        <v>177</v>
+      </c>
+      <c r="D36" s="3">
+        <v>1090</v>
+      </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
+      <c r="B37" s="4">
+        <v>4225</v>
+      </c>
+      <c r="C37" s="4">
+        <v>646</v>
+      </c>
+      <c r="D37" s="4">
+        <v>4871</v>
+      </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
+      <c r="B38" s="3">
+        <v>404</v>
+      </c>
+      <c r="C38" s="3">
+        <v>30</v>
+      </c>
+      <c r="D38" s="3">
+        <v>434</v>
+      </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
+      <c r="B39" s="4">
+        <v>107</v>
+      </c>
+      <c r="C39" s="4">
+        <v>129</v>
+      </c>
+      <c r="D39" s="4">
+        <v>236</v>
+      </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
@@ -8660,89 +8874,155 @@
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
+      <c r="B44" s="3">
+        <v>427</v>
+      </c>
+      <c r="C44" s="3">
+        <v>55</v>
+      </c>
+      <c r="D44" s="3">
+        <v>482</v>
+      </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
+      <c r="B45" s="4">
+        <v>1710</v>
+      </c>
+      <c r="C45" s="4">
+        <v>506</v>
+      </c>
+      <c r="D45" s="4">
+        <v>2216</v>
+      </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
+      <c r="B46" s="3">
+        <v>4010</v>
+      </c>
+      <c r="C46" s="3">
+        <v>737</v>
+      </c>
+      <c r="D46" s="3">
+        <v>4747</v>
+      </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
+      <c r="B47" s="4">
+        <v>2212</v>
+      </c>
+      <c r="C47" s="4">
+        <v>224</v>
+      </c>
+      <c r="D47" s="4">
+        <v>2436</v>
+      </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
+      <c r="B48" s="3">
+        <v>737</v>
+      </c>
+      <c r="C48" s="3">
+        <v>293</v>
+      </c>
+      <c r="D48" s="3">
+        <v>1030</v>
+      </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
+      <c r="B49" s="4">
+        <v>3717</v>
+      </c>
+      <c r="C49" s="4">
+        <v>942</v>
+      </c>
+      <c r="D49" s="4">
+        <v>4659</v>
+      </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
+      <c r="B50" s="3">
+        <v>357</v>
+      </c>
+      <c r="C50" s="3">
+        <v>93</v>
+      </c>
+      <c r="D50" s="3">
+        <v>450</v>
+      </c>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
+      <c r="B51" s="4">
+        <v>815</v>
+      </c>
+      <c r="C51" s="4">
+        <v>319</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1134</v>
+      </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
+      <c r="B52" s="3">
+        <v>108</v>
+      </c>
+      <c r="C52" s="3">
+        <v>26</v>
+      </c>
+      <c r="D52" s="3">
+        <v>134</v>
+      </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
+      <c r="B53" s="4">
+        <v>97</v>
+      </c>
+      <c r="C53" s="4">
+        <v>36</v>
+      </c>
+      <c r="D53" s="4">
+        <v>133</v>
+      </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
+      <c r="B54" s="3">
+        <v>365</v>
+      </c>
+      <c r="C54" s="3">
+        <v>304</v>
+      </c>
+      <c r="D54" s="3">
+        <v>669</v>
+      </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
@@ -8750,15 +9030,15 @@
       </c>
       <c r="B55" s="6">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>0</v>
+        <v>1134</v>
       </c>
       <c r="C55" s="6">
         <f t="shared" ref="C55:D55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
